--- a/data/trending_integrated_20260922_10.xlsx
+++ b/data/trending_integrated_20260922_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z17"/>
+  <dimension ref="A1:Z20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>0.04</v>
       </c>
       <c r="E2" t="n">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F2" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="G2" t="n">
-        <v>122</v>
+        <v>151</v>
       </c>
       <c r="H2" t="n">
         <v>0.6899999999999999</v>
@@ -610,7 +610,7 @@
         <v>0.65</v>
       </c>
       <c r="O2" t="n">
-        <v>34829328240</v>
+        <v>34865926890</v>
       </c>
       <c r="P2" t="n">
         <v>65300</v>
@@ -626,12 +626,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>국산 NPU 기반 휴머노이드 개발 착수 및 인텔, AMD와의 파트너십 관련 긍정적 뉴스. AI 반도체 기술 기반의 성장 전망.</t>
+          <t>국산 NPU 기반 휴머노이드 개발 및 AI 반도체 파트너십 관련 뉴스. 높은 기술력 대비 실적 부재 및 주가 변동성.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -670,13 +670,13 @@
         <v>-0.22</v>
       </c>
       <c r="E3" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F3" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G3" t="n">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="H3" t="n">
         <v>0.48</v>
@@ -702,7 +702,7 @@
         <v>0.7</v>
       </c>
       <c r="O3" t="n">
-        <v>5200737889</v>
+        <v>5230868829</v>
       </c>
       <c r="P3" t="n">
         <v>4760</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>모든 악재 해소 후 상승 기대. K-바이오 및 항암 백신 관련 긍정적 전망.</t>
+          <t>악재 해소 및 K-바이오 섹터 상승 기대감. 기관 투자자 지분 확보 및 공매도 상환 압박 분석.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['항암 백신', 'K-바이오', '기관 투자자']</t>
+          <t>['K-바이오', '기관 투자자', '공매도']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>66600</v>
+        <v>66900</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+27.34%</t>
+          <t>'+27.92%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F4" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G4" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="H4" t="n">
         <v>6.87</v>
@@ -794,7 +794,7 @@
         <v>6.88</v>
       </c>
       <c r="O4" t="n">
-        <v>104905988450</v>
+        <v>108637534650</v>
       </c>
       <c r="P4" t="n">
         <v>148300</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>큰 폭의 상승세를 보이며 전고점 돌파 기대. 반도체 섹터 내 키 맞추기 움직임.</t>
+          <t>반도체 업황 개선 및 키맞추기 장세 속 급등. 20일선 안착 여부 주목. 상한가 기대감.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['반도체', '전고점 돌파', '상승세']</t>
+          <t>['반도체', '키맞추기', '급등']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>대덕전자</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32500</v>
+        <v>116300</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+9.43%</t>
+          <t>'+14.13%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.62</v>
+        <v>-0.12</v>
       </c>
       <c r="E5" t="n">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="F5" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="G5" t="n">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="H5" t="n">
-        <v>11.3</v>
+        <v>18.2</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>29700</v>
+        <v>101900</v>
       </c>
       <c r="K5" t="n">
-        <v>30500</v>
+        <v>110000</v>
       </c>
       <c r="L5" t="n">
-        <v>33450</v>
+        <v>120700</v>
       </c>
       <c r="M5" t="n">
-        <v>30000</v>
+        <v>109800</v>
       </c>
       <c r="N5" t="n">
-        <v>11.92</v>
+        <v>18.32</v>
       </c>
       <c r="O5" t="n">
-        <v>180014331200</v>
+        <v>212209003250</v>
       </c>
       <c r="P5" t="n">
-        <v>75900</v>
+        <v>198000</v>
       </c>
       <c r="Q5" t="n">
-        <v>15000</v>
+        <v>26350</v>
       </c>
       <c r="R5" t="n">
-        <v>351000</v>
+        <v>213000</v>
       </c>
       <c r="S5" t="n">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>가온전선과의 비교 속 대한전선의 상승 기대감. 4분기 이후 전력 인프라 중심 이동 전망.</t>
+          <t>SK하이닉스 GDDR7 수혜 기대감에 따른 주가 급등. 코리아써키트 등 경쟁사 동향 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['전력 인프라', '거래량', '신고점']</t>
+          <t>['GDDR7', 'SK하이닉스', '수혜주']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>353200</t>
         </is>
       </c>
     </row>
@@ -935,21 +935,21 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6350</v>
+        <v>6390</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+8.36%</t>
+          <t>'+9.04%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.19</v>
       </c>
       <c r="E6" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F6" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G6" t="n">
         <v>94</v>
@@ -978,7 +978,7 @@
         <v>0.19</v>
       </c>
       <c r="O6" t="n">
-        <v>43818087105</v>
+        <v>45129757590</v>
       </c>
       <c r="P6" t="n">
         <v>13140</v>
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>337250</v>
+        <v>32325</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+5.89%</t>
+          <t>'+8.84%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.4</v>
+        <v>-0.62</v>
       </c>
       <c r="E7" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F7" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G7" t="n">
-        <v>188</v>
+        <v>102</v>
       </c>
       <c r="H7" t="n">
-        <v>3.22</v>
+        <v>11.3</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>318500</v>
+        <v>29700</v>
       </c>
       <c r="K7" t="n">
-        <v>333000</v>
+        <v>30500</v>
       </c>
       <c r="L7" t="n">
-        <v>349500</v>
+        <v>33450</v>
       </c>
       <c r="M7" t="n">
-        <v>325000</v>
+        <v>30000</v>
       </c>
       <c r="N7" t="n">
-        <v>3.62</v>
+        <v>11.92</v>
       </c>
       <c r="O7" t="n">
-        <v>86107887750</v>
+        <v>186776409325</v>
       </c>
       <c r="P7" t="n">
-        <v>635000</v>
+        <v>75900</v>
       </c>
       <c r="Q7" t="n">
-        <v>52600</v>
+        <v>15000</v>
       </c>
       <c r="R7" t="n">
-        <v>3000</v>
+        <v>351000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>구리 가격 상승 및 신고가 랠리에 대한 기대감. 외인 지분 유입과 나스닥 폭등 등 긍정적 시장 상황 반영.</t>
+          <t>전선주 대장 탈환 기대감 속 거래량 증가. 4분기 이후 전력 인프라 투자 확대 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['신고가', '구리품귀', '우상향']</t>
+          <t>['전력 인프라', '거래량', '대장주']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,77 +1108,77 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>SFA반도체</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13400</v>
+        <v>10990</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.40%</t>
+          <t>'+4.17%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="E8" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F8" t="n">
         <v>31</v>
       </c>
       <c r="G8" t="n">
-        <v>167</v>
+        <v>96</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>12960</v>
+        <v>10550</v>
       </c>
       <c r="K8" t="n">
-        <v>13500</v>
+        <v>10730</v>
       </c>
       <c r="L8" t="n">
-        <v>14190</v>
+        <v>11000</v>
       </c>
       <c r="M8" t="n">
-        <v>13370</v>
+        <v>10300</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="O8" t="n">
-        <v>16008637065</v>
+        <v>67934953600</v>
       </c>
       <c r="P8" t="n">
-        <v>19380</v>
+        <v>11640</v>
       </c>
       <c r="Q8" t="n">
-        <v>3200</v>
+        <v>3735</v>
       </c>
       <c r="R8" t="n">
-        <v>-40000</v>
+        <v>-140000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>광주 삼성전자 공장 착공 소식에 따른 기대감. 주가 부양 및 호황 전망.</t>
+          <t>반도체 후공정 섹터 내 조정 후 반등 기대감. 외인 매도세에도 불구하고 강한 흐름 유지.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['삼성전자', '공장 착공', '호황']</t>
+          <t>['후공정', '반도체', '반등']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>036540</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1921500</v>
+        <v>331500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+2.86%</t>
+          <t>'+4.08%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.06</v>
+        <v>-0.4</v>
       </c>
       <c r="E9" t="n">
-        <v>680</v>
+        <v>76</v>
       </c>
       <c r="F9" t="n">
-        <v>417</v>
+        <v>57</v>
       </c>
       <c r="G9" t="n">
-        <v>3196</v>
+        <v>198</v>
       </c>
       <c r="H9" t="n">
-        <v>50.17</v>
+        <v>3.22</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1868000</v>
+        <v>318500</v>
       </c>
       <c r="K9" t="n">
-        <v>1909000</v>
+        <v>333000</v>
       </c>
       <c r="L9" t="n">
-        <v>1935000</v>
+        <v>349500</v>
       </c>
       <c r="M9" t="n">
-        <v>1904000</v>
+        <v>325000</v>
       </c>
       <c r="N9" t="n">
-        <v>50.23</v>
+        <v>3.62</v>
       </c>
       <c r="O9" t="n">
-        <v>1459050561500</v>
+        <v>89564321750</v>
       </c>
       <c r="P9" t="n">
-        <v>2987000</v>
+        <v>635000</v>
       </c>
       <c r="Q9" t="n">
-        <v>333000</v>
+        <v>52600</v>
       </c>
       <c r="R9" t="n">
-        <v>85000</v>
+        <v>3000</v>
       </c>
       <c r="S9" t="n">
-        <v>55000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>AI 반도체 주 강세 및 뉴욕 증시 급등에 따른 SK하이닉스 주가 상승 기대.</t>
+          <t>신고가 경신 기대감과 함께 강한 우상향 추세 분석. 구리 가격 상승 및 글로벌 증시 호조세 영향.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['AI', '반도체', '뉴욕증시']</t>
+          <t>['신고가', '정배열', '성장동력']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>76</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>000500</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18800</v>
+        <v>13370</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.79%</t>
+          <t>'+3.16%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.27</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="F10" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G10" t="n">
-        <v>294</v>
+        <v>173</v>
       </c>
       <c r="H10" t="n">
-        <v>10.47</v>
+        <v>0</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>18290</v>
+        <v>12960</v>
       </c>
       <c r="K10" t="n">
-        <v>18830</v>
+        <v>13500</v>
       </c>
       <c r="L10" t="n">
-        <v>19540</v>
+        <v>14190</v>
       </c>
       <c r="M10" t="n">
-        <v>18560</v>
+        <v>13290</v>
       </c>
       <c r="N10" t="n">
-        <v>10.74</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>67488093095</v>
+        <v>16957656000</v>
       </c>
       <c r="P10" t="n">
-        <v>40350</v>
+        <v>19380</v>
       </c>
       <c r="Q10" t="n">
-        <v>3320</v>
+        <v>3200</v>
       </c>
       <c r="R10" t="n">
-        <v>5000</v>
+        <v>-40000</v>
       </c>
       <c r="S10" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>공매도 세력에 대한 비판과 함께 주가 상승 기대감. 체코 원전 수주 관련 긍정적 전망.</t>
+          <t>광주 삼성전자 플렉트 공장 착공 소식에 따른 기대감. 매출액 증가 및 호남 지역 투자 확대 전망.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['공매도', '원전 수주', '주가 상승']</t>
+          <t>['삼성전자', '플렉트 공장', '광주']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>280500</v>
+        <v>1920000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.37%</t>
+          <t>'+2.78%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.1</v>
+        <v>-0.06</v>
       </c>
       <c r="E11" t="n">
-        <v>776</v>
+        <v>705</v>
       </c>
       <c r="F11" t="n">
-        <v>484</v>
+        <v>429</v>
       </c>
       <c r="G11" t="n">
-        <v>4249</v>
+        <v>3289</v>
       </c>
       <c r="H11" t="n">
-        <v>46.56</v>
+        <v>50.17</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>274000</v>
+        <v>1868000</v>
       </c>
       <c r="K11" t="n">
-        <v>283000</v>
+        <v>1909000</v>
       </c>
       <c r="L11" t="n">
-        <v>283500</v>
+        <v>1935000</v>
       </c>
       <c r="M11" t="n">
-        <v>279500</v>
+        <v>1904000</v>
       </c>
       <c r="N11" t="n">
-        <v>46.46</v>
+        <v>50.23</v>
       </c>
       <c r="O11" t="n">
-        <v>1144533638000</v>
+        <v>1562740170000</v>
       </c>
       <c r="P11" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q11" t="n">
-        <v>81100</v>
+        <v>333000</v>
       </c>
       <c r="R11" t="n">
-        <v>26000</v>
+        <v>85000</v>
       </c>
       <c r="S11" t="n">
-        <v>42000</v>
+        <v>55000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>3분기 영업이익 호조 및 30만 전자 돌파 기대감. 미 증시 반도체주 급등.</t>
+          <t>AI 반도체 주 강세 및 뉴욕 증시 급등에 따른 SK하이닉스 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['영업이익', '반도체', '미증시']</t>
+          <t>['AI', '반도체', '뉴욕증시']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>86200</v>
+        <v>18710</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+1.06%</t>
+          <t>'+2.30%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.27</v>
       </c>
       <c r="E12" t="n">
-        <v>139</v>
+        <v>75</v>
       </c>
       <c r="F12" t="n">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="G12" t="n">
-        <v>565</v>
+        <v>315</v>
       </c>
       <c r="H12" t="n">
-        <v>23.05</v>
+        <v>10.47</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>85300</v>
+        <v>18290</v>
       </c>
       <c r="K12" t="n">
-        <v>87000</v>
+        <v>18830</v>
       </c>
       <c r="L12" t="n">
-        <v>87000</v>
+        <v>19540</v>
       </c>
       <c r="M12" t="n">
-        <v>85500</v>
+        <v>18560</v>
       </c>
       <c r="N12" t="n">
-        <v>23.12</v>
+        <v>10.74</v>
       </c>
       <c r="O12" t="n">
-        <v>48720305500</v>
+        <v>69453048290</v>
       </c>
       <c r="P12" t="n">
-        <v>139200</v>
+        <v>40350</v>
       </c>
       <c r="Q12" t="n">
-        <v>57000</v>
+        <v>3320</v>
       </c>
       <c r="R12" t="n">
-        <v>-160000</v>
+        <v>5000</v>
       </c>
       <c r="S12" t="n">
-        <v>-6000</v>
+        <v>15000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 투자 관련 공급 계약 체결 및 SMR 추진 확정 등 긍정적 공시 및 뉴스. 하지만 공매도 이슈와 관련된 부정적 심리도 공존.</t>
+          <t>체코 원전 수주 기대감 속 공매도 관련 언급 및 주가 방어 의혹 제기. 5만원 목표 제시.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['SMR', '공급계약', '공매도']</t>
+          <t>['체코 원전', '공매도', '수주']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17790</v>
+        <v>280000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+0.40%</t>
+          <t>'+2.19%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-1.68</v>
+        <v>0.1</v>
       </c>
       <c r="E13" t="n">
-        <v>121</v>
+        <v>795</v>
       </c>
       <c r="F13" t="n">
-        <v>75</v>
+        <v>495</v>
       </c>
       <c r="G13" t="n">
-        <v>500</v>
+        <v>4302</v>
       </c>
       <c r="H13" t="n">
-        <v>6.22</v>
+        <v>46.56</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>17720</v>
+        <v>274000</v>
       </c>
       <c r="K13" t="n">
-        <v>18230</v>
+        <v>283000</v>
       </c>
       <c r="L13" t="n">
-        <v>18750</v>
+        <v>283500</v>
       </c>
       <c r="M13" t="n">
-        <v>17500</v>
+        <v>279500</v>
       </c>
       <c r="N13" t="n">
-        <v>7.9</v>
+        <v>46.46</v>
       </c>
       <c r="O13" t="n">
-        <v>104224308155</v>
+        <v>1208114534750</v>
       </c>
       <c r="P13" t="n">
-        <v>31500</v>
+        <v>374500</v>
       </c>
       <c r="Q13" t="n">
-        <v>1272</v>
+        <v>81100</v>
       </c>
       <c r="R13" t="n">
-        <v>-359000</v>
+        <v>26000</v>
       </c>
       <c r="S13" t="n">
-        <v>5000</v>
+        <v>42000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 광통신 섹터 강세에 따른 동반 상승 기대. AI 데이터 관련 낙관론.</t>
+          <t>3분기 영업이익 호조 및 30만 전자 돌파 기대감. 미 증시 반도체주 급등.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['광통신', 'AI 데이터', '상한가']</t>
+          <t>['영업이익', '반도체', '미증시']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>20</v>
+        <v>111</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,90 +1660,90 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8470</v>
+        <v>17920</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-0.59%</t>
+          <t>'+1.13%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.01</v>
+        <v>-1.68</v>
       </c>
       <c r="E14" t="n">
-        <v>51</v>
+        <v>124</v>
       </c>
       <c r="F14" t="n">
-        <v>28</v>
+        <v>77</v>
       </c>
       <c r="G14" t="n">
-        <v>165</v>
+        <v>516</v>
       </c>
       <c r="H14" t="n">
-        <v>26.58</v>
+        <v>6.22</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>8520</v>
+        <v>17720</v>
       </c>
       <c r="K14" t="n">
-        <v>8620</v>
+        <v>18230</v>
       </c>
       <c r="L14" t="n">
-        <v>8650</v>
+        <v>18750</v>
       </c>
       <c r="M14" t="n">
-        <v>8460</v>
+        <v>17500</v>
       </c>
       <c r="N14" t="n">
-        <v>26.57</v>
+        <v>7.9</v>
       </c>
       <c r="O14" t="n">
-        <v>8292852410</v>
+        <v>109069878750</v>
       </c>
       <c r="P14" t="n">
-        <v>17950</v>
+        <v>31500</v>
       </c>
       <c r="Q14" t="n">
-        <v>8120</v>
+        <v>1272</v>
       </c>
       <c r="R14" t="n">
-        <v>-212000</v>
+        <v>-359000</v>
       </c>
       <c r="S14" t="n">
-        <v>7000</v>
+        <v>5000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>장기 소외주로 분류되며 비전 부족. 낮은 실적과 경영진 능력에 대한 부정적 평가.</t>
+          <t>미국 광통신 섹터 강세에 따른 동반 상승 기대. AI 데이터 관련 낙관론.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['장기 소외주', '비전 부족', '경영진']</t>
+          <t>['광통신', 'AI 데이터', '상한가']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,90 +1752,90 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3955</v>
+        <v>85700</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-2.47%</t>
+          <t>'+0.47%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.63</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>47</v>
+        <v>140</v>
       </c>
       <c r="F15" t="n">
-        <v>37</v>
+        <v>93</v>
       </c>
       <c r="G15" t="n">
-        <v>193</v>
+        <v>590</v>
       </c>
       <c r="H15" t="n">
-        <v>0.96</v>
+        <v>23.05</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>4055</v>
+        <v>85300</v>
       </c>
       <c r="K15" t="n">
-        <v>4080</v>
+        <v>87000</v>
       </c>
       <c r="L15" t="n">
-        <v>4080</v>
+        <v>87000</v>
       </c>
       <c r="M15" t="n">
-        <v>3850</v>
+        <v>85500</v>
       </c>
       <c r="N15" t="n">
-        <v>0.33</v>
+        <v>23.12</v>
       </c>
       <c r="O15" t="n">
-        <v>6586712555</v>
+        <v>51937734150</v>
       </c>
       <c r="P15" t="n">
-        <v>6480</v>
+        <v>139200</v>
       </c>
       <c r="Q15" t="n">
-        <v>1738</v>
+        <v>57000</v>
       </c>
       <c r="R15" t="n">
-        <v>-44000</v>
+        <v>-160000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-6000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>암호화폐 시장의 전반적인 강세장이 미투온의 주가에도 긍정적인 영향을 미칠 것이라는 기대감.</t>
+          <t>차세대 원자력 및 방산 사업 계약 체결 확정. 대규모 투자 유치 기대감과 함께 공매도 관련 논란.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['텐베거', '차트분석', '폭등장세']</t>
+          <t>['SMR', '공급 계약', '공매도']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,90 +1844,90 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>24600</v>
+        <v>8500</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-2.57%</t>
+          <t>'-0.23%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.41</v>
+        <v>0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="F16" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G16" t="n">
-        <v>93</v>
+        <v>178</v>
       </c>
       <c r="H16" t="n">
-        <v>1.76</v>
+        <v>26.58</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>25250</v>
+        <v>8520</v>
       </c>
       <c r="K16" t="n">
-        <v>26150</v>
+        <v>8620</v>
       </c>
       <c r="L16" t="n">
-        <v>26600</v>
+        <v>8650</v>
       </c>
       <c r="M16" t="n">
-        <v>24250</v>
+        <v>8410</v>
       </c>
       <c r="N16" t="n">
-        <v>0.35</v>
+        <v>26.57</v>
       </c>
       <c r="O16" t="n">
-        <v>72737850750</v>
+        <v>10788868100</v>
       </c>
       <c r="P16" t="n">
-        <v>39350</v>
+        <v>17950</v>
       </c>
       <c r="Q16" t="n">
-        <v>8200</v>
+        <v>8120</v>
       </c>
       <c r="R16" t="n">
-        <v>-10000</v>
+        <v>-212000</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>타임지 선정 및 연상 기대감. 프로그램 매집 신호 포착.</t>
+          <t>적자 지속 및 주가 부진에 대한 불만 제기. 반도체 섹터 내 부진한 흐름 지속. 외인 매도세.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['타임지 선정', '연상', '프로그램 매집']</t>
+          <t>['적자', '주가 부진', '외인 매도']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,97 +1936,373 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10710</v>
+        <v>21300</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-3.16%</t>
+          <t>'-0.93%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.4</v>
+        <v>-0.05</v>
       </c>
       <c r="E17" t="n">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="F17" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G17" t="n">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="H17" t="n">
-        <v>17.89</v>
+        <v>1.2</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>11060</v>
+        <v>21500</v>
       </c>
       <c r="K17" t="n">
-        <v>10570</v>
+        <v>21200</v>
       </c>
       <c r="L17" t="n">
-        <v>10720</v>
+        <v>22900</v>
       </c>
       <c r="M17" t="n">
-        <v>10060</v>
+        <v>20850</v>
       </c>
       <c r="N17" t="n">
-        <v>18.29</v>
+        <v>1.25</v>
       </c>
       <c r="O17" t="n">
-        <v>24070387805</v>
+        <v>37778229875</v>
       </c>
       <c r="P17" t="n">
-        <v>22450</v>
+        <v>22900</v>
       </c>
       <c r="Q17" t="n">
-        <v>1760</v>
+        <v>9900</v>
       </c>
       <c r="R17" t="n">
-        <v>3000</v>
+        <v>89000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>투자 경고 종목 지정 및 주가 하락 우려. '개잡주'로 분류되며 부정적 전망.</t>
+          <t>글로벌 제약사 (모더나, 머크) 임상 및 투자 소식에 따른 기대감. 반도체 시장 강세와 수급 경쟁 우려.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>['임상3상', '반도체', '외국인']</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>950260</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>미투온</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>3925</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>'-3.21%</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E18" t="n">
+        <v>48</v>
+      </c>
+      <c r="F18" t="n">
+        <v>37</v>
+      </c>
+      <c r="G18" t="n">
+        <v>204</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>4055</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4080</v>
+      </c>
+      <c r="L18" t="n">
+        <v>4080</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3850</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="O18" t="n">
+        <v>6823193575</v>
+      </c>
+      <c r="P18" t="n">
+        <v>6480</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1738</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-44000</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>가상화폐 시장 강세 전망에 따른 기대감. 그러나 명확한 근거 부족 및 주가 하락 추세.</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
         <v>0.1</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>['투자경고', '주가 하락', '개잡주']</t>
-        </is>
-      </c>
-      <c r="X17" t="n">
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>['텐베거', '챠트분석', '코인주']</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>201490</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>스카이랩스</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>24300</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>'-3.76%</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="E19" t="n">
+        <v>55</v>
+      </c>
+      <c r="F19" t="n">
+        <v>36</v>
+      </c>
+      <c r="G19" t="n">
+        <v>100</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>25250</v>
+      </c>
+      <c r="K19" t="n">
+        <v>26150</v>
+      </c>
+      <c r="L19" t="n">
+        <v>26600</v>
+      </c>
+      <c r="M19" t="n">
+        <v>24050</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O19" t="n">
+        <v>77156634425</v>
+      </c>
+      <c r="P19" t="n">
+        <v>39350</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>8200</v>
+      </c>
+      <c r="R19" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>코스닥 역사 쓸 종목으로 평가되며 연상 기대감. 프로그램 매집 확인 및 매물 소화 중.</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>['연상', '매물 소화', '프로그램 매집']</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>386380</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>광전자</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>10520</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>'-4.88%</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E20" t="n">
+        <v>66</v>
+      </c>
+      <c r="F20" t="n">
+        <v>47</v>
+      </c>
+      <c r="G20" t="n">
+        <v>155</v>
+      </c>
+      <c r="H20" t="n">
+        <v>17.89</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>11060</v>
+      </c>
+      <c r="K20" t="n">
+        <v>10570</v>
+      </c>
+      <c r="L20" t="n">
+        <v>10815</v>
+      </c>
+      <c r="M20" t="n">
+        <v>10060</v>
+      </c>
+      <c r="N20" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="O20" t="n">
+        <v>26656375000</v>
+      </c>
+      <c r="P20" t="n">
+        <v>22450</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1760</v>
+      </c>
+      <c r="R20" t="n">
+        <v>3000</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>투자 경고 종목 지정 및 주가 하락세 지속. 미래 먹거리 관련 언급 있으나 실질적 근거 부족.</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>['투자경고', '주가 하락', '미래 먹거리']</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
         <v>7</v>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>017900</t>
         </is>

--- a/data/trending_integrated_20260922_10.xlsx
+++ b/data/trending_integrated_20260922_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z20"/>
+  <dimension ref="A1:Z22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>0.04</v>
       </c>
       <c r="E2" t="n">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="F2" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="G2" t="n">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="H2" t="n">
         <v>0.6899999999999999</v>
@@ -610,7 +610,7 @@
         <v>0.65</v>
       </c>
       <c r="O2" t="n">
-        <v>34865926890</v>
+        <v>34875939090</v>
       </c>
       <c r="P2" t="n">
         <v>65300</v>
@@ -626,12 +626,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>국산 NPU 기반 휴머노이드 개발 및 AI 반도체 파트너십 관련 뉴스. 높은 기술력 대비 실적 부재 및 주가 변동성.</t>
+          <t>노타의 국산 NPU 기반 휴머노이드 개발 착수 및 AI 반도체 파트너십 부각. 로봇 속도 3배 초가속 관련 기술력 강조.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
         <v>29</v>
       </c>
       <c r="G3" t="n">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="H3" t="n">
         <v>0.48</v>
@@ -702,7 +702,7 @@
         <v>0.7</v>
       </c>
       <c r="O3" t="n">
-        <v>5230868829</v>
+        <v>5249119339</v>
       </c>
       <c r="P3" t="n">
         <v>4760</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>66900</v>
+        <v>66100</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+27.92%</t>
+          <t>'+26.39%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F4" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G4" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="H4" t="n">
         <v>6.87</v>
@@ -794,7 +794,7 @@
         <v>6.88</v>
       </c>
       <c r="O4" t="n">
-        <v>108637534650</v>
+        <v>111853979050</v>
       </c>
       <c r="P4" t="n">
         <v>148300</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>반도체 업황 개선 및 키맞추기 장세 속 급등. 20일선 안착 여부 주목. 상한가 기대감.</t>
+          <t>상한가 기록 및 27% 급등에 대한 환호, 6만원 위 매도 의견 및 반도체 장기 투자 부정론 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['반도체', '키맞추기', '급등']</t>
+          <t>['반도체', '급등주']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>116300</v>
+        <v>114200</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+14.13%</t>
+          <t>'+12.07%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.12</v>
       </c>
       <c r="E5" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="F5" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H5" t="n">
         <v>18.2</v>
@@ -886,7 +886,7 @@
         <v>18.32</v>
       </c>
       <c r="O5" t="n">
-        <v>212209003250</v>
+        <v>224967457300</v>
       </c>
       <c r="P5" t="n">
         <v>198000</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>SK하이닉스 GDDR7 수혜 기대감에 따른 주가 급등. 코리아써키트 등 경쟁사 동향 언급.</t>
+          <t>SK하이닉스 GDDR7 공급망 수혜 기대감 및 110,000원대 허리 구간 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['GDDR7', 'SK하이닉스', '수혜주']</t>
+          <t>['PCB', '반도체 소재']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6390</v>
+        <v>6340</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+9.04%</t>
+          <t>'+8.19%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.19</v>
       </c>
       <c r="E6" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F6" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G6" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>0.19</v>
       </c>
       <c r="O6" t="n">
-        <v>45129757590</v>
+        <v>46305333975</v>
       </c>
       <c r="P6" t="n">
         <v>13140</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>비트코인 급등과 함께 코인 테마주로서 강세. 불확실성 해소 및 신고가 기대.</t>
+          <t>비트코인 급등과 가상화폐 테마의 반란으로 인한 우리기술투자의 강세 전망. 공개매수 진행 및 외인 매수세 유입 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['비트코인', '코인 테마', '신고가']</t>
+          <t>['비트코인', '가상화폐', '공개매수']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32325</v>
+        <v>32100</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+8.84%</t>
+          <t>'+8.08%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.62</v>
       </c>
       <c r="E7" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F7" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G7" t="n">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="H7" t="n">
         <v>11.3</v>
@@ -1070,7 +1070,7 @@
         <v>11.92</v>
       </c>
       <c r="O7" t="n">
-        <v>186776409325</v>
+        <v>198109142550</v>
       </c>
       <c r="P7" t="n">
         <v>75900</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>전선주 대장 탈환 기대감 속 거래량 증가. 4분기 이후 전력 인프라 투자 확대 전망.</t>
+          <t>가온전선과의 비교 속에서 700원 벽 돌파 실패 및 단기 목표가 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['전력 인프라', '거래량', '대장주']</t>
+          <t>['전선주', '주가 전망']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,31 +1115,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SFA반도체</t>
+          <t>KBI메탈</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10990</v>
+        <v>6560</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+4.17%</t>
+          <t>'+3.96%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.01</v>
+        <v>-0.09</v>
       </c>
       <c r="E8" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F8" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G8" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H8" t="n">
-        <v>9.609999999999999</v>
+        <v>4.86</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,47 +1147,47 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>10550</v>
+        <v>6310</v>
       </c>
       <c r="K8" t="n">
-        <v>10730</v>
+        <v>6460</v>
       </c>
       <c r="L8" t="n">
-        <v>11000</v>
+        <v>7090</v>
       </c>
       <c r="M8" t="n">
-        <v>10300</v>
+        <v>6350</v>
       </c>
       <c r="N8" t="n">
-        <v>8.6</v>
+        <v>4.95</v>
       </c>
       <c r="O8" t="n">
-        <v>67934953600</v>
+        <v>43924102880</v>
       </c>
       <c r="P8" t="n">
-        <v>11640</v>
+        <v>11760</v>
       </c>
       <c r="Q8" t="n">
-        <v>3735</v>
+        <v>1620</v>
       </c>
       <c r="R8" t="n">
-        <v>-140000</v>
+        <v>54000</v>
       </c>
       <c r="S8" t="n">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>반도체 후공정 섹터 내 조정 후 반등 기대감. 외인 매도세에도 불구하고 강한 흐름 유지.</t>
+          <t>KBI메탈의 매집 및 시총 가벼움은 긍정적이나, 외인 물량 폭탄 매도 및 추격 매수 경고. 전쟁 확산 가능성 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['후공정', '반도체', '반등']</t>
+          <t>['매집', '외인매도', '전쟁주']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>036540</t>
+          <t>024840</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>331500</v>
+        <v>14050</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.08%</t>
+          <t>'+3.77%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.4</v>
+        <v>-0.34</v>
       </c>
       <c r="E9" t="n">
-        <v>76</v>
+        <v>41</v>
       </c>
       <c r="F9" t="n">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="G9" t="n">
-        <v>198</v>
+        <v>69</v>
       </c>
       <c r="H9" t="n">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,47 +1239,47 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>318500</v>
+        <v>13540</v>
       </c>
       <c r="K9" t="n">
-        <v>333000</v>
+        <v>13870</v>
       </c>
       <c r="L9" t="n">
-        <v>349500</v>
+        <v>14650</v>
       </c>
       <c r="M9" t="n">
-        <v>325000</v>
+        <v>13740</v>
       </c>
       <c r="N9" t="n">
-        <v>3.62</v>
+        <v>3.68</v>
       </c>
       <c r="O9" t="n">
-        <v>89564321750</v>
+        <v>77795417365</v>
       </c>
       <c r="P9" t="n">
-        <v>635000</v>
+        <v>20300</v>
       </c>
       <c r="Q9" t="n">
-        <v>52600</v>
+        <v>2885</v>
       </c>
       <c r="R9" t="n">
-        <v>3000</v>
+        <v>236000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>신고가 경신 기대감과 함께 강한 우상향 추세 분석. 구리 가격 상승 및 글로벌 증시 호조세 영향.</t>
+          <t>AI 시대 전력망 중요성 언급 및 대한전선과의 비교 속에서 15000원대 탈출 목표 제시.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['신고가', '정배열', '성장동력']</t>
+          <t>['전력망', '테마주']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>006340</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13370</v>
+        <v>330500</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.16%</t>
+          <t>'+3.77%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="E10" t="n">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="F10" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="G10" t="n">
-        <v>173</v>
+        <v>203</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,38 +1331,38 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>12960</v>
+        <v>318500</v>
       </c>
       <c r="K10" t="n">
-        <v>13500</v>
+        <v>333000</v>
       </c>
       <c r="L10" t="n">
-        <v>14190</v>
+        <v>349500</v>
       </c>
       <c r="M10" t="n">
-        <v>13290</v>
+        <v>325000</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="O10" t="n">
-        <v>16957656000</v>
+        <v>92750109750</v>
       </c>
       <c r="P10" t="n">
-        <v>19380</v>
+        <v>635000</v>
       </c>
       <c r="Q10" t="n">
-        <v>3200</v>
+        <v>52600</v>
       </c>
       <c r="R10" t="n">
-        <v>-40000</v>
+        <v>3000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>광주 삼성전자 플렉트 공장 착공 소식에 따른 기대감. 매출액 증가 및 호남 지역 투자 확대 전망.</t>
+          <t>나스닥 폭등 및 구리 가격 상승에 따른 가온전선의 신고가 경신 및 추가 상승 전망. 외인 지분율 확대 및 성장 동력 기대.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,11 +1371,11 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['삼성전자', '플렉트 공장', '광주']</t>
+          <t>['나스닥', '구리', '신고가']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>000500</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1920000</v>
+        <v>1918000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.78%</t>
+          <t>'+2.68%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.06</v>
       </c>
       <c r="E11" t="n">
-        <v>705</v>
+        <v>730</v>
       </c>
       <c r="F11" t="n">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="G11" t="n">
-        <v>3289</v>
+        <v>3350</v>
       </c>
       <c r="H11" t="n">
         <v>50.17</v>
@@ -1438,7 +1438,7 @@
         <v>50.23</v>
       </c>
       <c r="O11" t="n">
-        <v>1562740170000</v>
+        <v>1689036804500</v>
       </c>
       <c r="P11" t="n">
         <v>2987000</v>
@@ -1483,31 +1483,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18710</v>
+        <v>13280</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.30%</t>
+          <t>'+2.47%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.27</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="F12" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="G12" t="n">
-        <v>315</v>
+        <v>189</v>
       </c>
       <c r="H12" t="n">
-        <v>10.47</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>18290</v>
+        <v>12960</v>
       </c>
       <c r="K12" t="n">
-        <v>18830</v>
+        <v>13500</v>
       </c>
       <c r="L12" t="n">
-        <v>19540</v>
+        <v>14190</v>
       </c>
       <c r="M12" t="n">
-        <v>18560</v>
+        <v>13270</v>
       </c>
       <c r="N12" t="n">
-        <v>10.74</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>69453048290</v>
+        <v>17464125000</v>
       </c>
       <c r="P12" t="n">
-        <v>40350</v>
+        <v>19380</v>
       </c>
       <c r="Q12" t="n">
-        <v>3320</v>
+        <v>3200</v>
       </c>
       <c r="R12" t="n">
-        <v>5000</v>
+        <v>-40000</v>
       </c>
       <c r="S12" t="n">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>체코 원전 수주 기대감 속 공매도 관련 언급 및 주가 방어 의혹 제기. 5만원 목표 제시.</t>
+          <t>광주 삼성전자 공장 착공 소식 및 호남 지역 호황 언급, 15000원대 물려있는 투자자들에 대한 우려 제기.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['체코 원전', '공매도', '수주']</t>
+          <t>['건설', '반도체 공장']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SFA반도체</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>280000</v>
+        <v>10810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.19%</t>
+          <t>'+2.46%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.1</v>
+        <v>1.01</v>
       </c>
       <c r="E13" t="n">
-        <v>795</v>
+        <v>43</v>
       </c>
       <c r="F13" t="n">
-        <v>495</v>
+        <v>31</v>
       </c>
       <c r="G13" t="n">
-        <v>4302</v>
+        <v>96</v>
       </c>
       <c r="H13" t="n">
-        <v>46.56</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>274000</v>
+        <v>10550</v>
       </c>
       <c r="K13" t="n">
-        <v>283000</v>
+        <v>10730</v>
       </c>
       <c r="L13" t="n">
-        <v>283500</v>
+        <v>11160</v>
       </c>
       <c r="M13" t="n">
-        <v>279500</v>
+        <v>10300</v>
       </c>
       <c r="N13" t="n">
-        <v>46.46</v>
+        <v>8.6</v>
       </c>
       <c r="O13" t="n">
-        <v>1208114534750</v>
+        <v>90001210565</v>
       </c>
       <c r="P13" t="n">
-        <v>374500</v>
+        <v>11640</v>
       </c>
       <c r="Q13" t="n">
-        <v>81100</v>
+        <v>3735</v>
       </c>
       <c r="R13" t="n">
-        <v>26000</v>
+        <v>-140000</v>
       </c>
       <c r="S13" t="n">
-        <v>42000</v>
+        <v>8000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>3분기 영업이익 호조 및 30만 전자 돌파 기대감. 미 증시 반도체주 급등.</t>
+          <t>반도체 조정 국면 속에서 2주간의 조정 이후 반등 기대감 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['영업이익', '반도체', '미증시']</t>
+          <t>['반도체', '조정']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>111</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,90 +1660,90 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>036540</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17920</v>
+        <v>279500</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+1.13%</t>
+          <t>'+2.01%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-1.68</v>
+        <v>0.1</v>
       </c>
       <c r="E14" t="n">
-        <v>124</v>
+        <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>77</v>
+        <v>493</v>
       </c>
       <c r="G14" t="n">
-        <v>516</v>
+        <v>3924</v>
       </c>
       <c r="H14" t="n">
-        <v>6.22</v>
+        <v>46.56</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>17720</v>
+        <v>274000</v>
       </c>
       <c r="K14" t="n">
-        <v>18230</v>
+        <v>283000</v>
       </c>
       <c r="L14" t="n">
-        <v>18750</v>
+        <v>283500</v>
       </c>
       <c r="M14" t="n">
-        <v>17500</v>
+        <v>279000</v>
       </c>
       <c r="N14" t="n">
-        <v>7.9</v>
+        <v>46.46</v>
       </c>
       <c r="O14" t="n">
-        <v>109069878750</v>
+        <v>1330659921250</v>
       </c>
       <c r="P14" t="n">
-        <v>31500</v>
+        <v>374500</v>
       </c>
       <c r="Q14" t="n">
-        <v>1272</v>
+        <v>81100</v>
       </c>
       <c r="R14" t="n">
-        <v>-359000</v>
+        <v>26000</v>
       </c>
       <c r="S14" t="n">
-        <v>5000</v>
+        <v>42000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미국 광통신 섹터 강세에 따른 동반 상승 기대. AI 데이터 관련 낙관론.</t>
+          <t>3분기 역대급 실적 기대감 속 30만원 돌파 및 미 증시 폭등 영향 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['광통신', 'AI 데이터', '상한가']</t>
+          <t>['반도체', '실적 전망']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>20</v>
+        <v>111</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>85700</v>
+        <v>18610</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+0.47%</t>
+          <t>'+1.75%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.27</v>
       </c>
       <c r="E15" t="n">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="F15" t="n">
-        <v>93</v>
+        <v>48</v>
       </c>
       <c r="G15" t="n">
-        <v>590</v>
+        <v>331</v>
       </c>
       <c r="H15" t="n">
-        <v>23.05</v>
+        <v>10.47</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,38 +1791,38 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>85300</v>
+        <v>18290</v>
       </c>
       <c r="K15" t="n">
-        <v>87000</v>
+        <v>18830</v>
       </c>
       <c r="L15" t="n">
-        <v>87000</v>
+        <v>19540</v>
       </c>
       <c r="M15" t="n">
-        <v>85500</v>
+        <v>18560</v>
       </c>
       <c r="N15" t="n">
-        <v>23.12</v>
+        <v>10.74</v>
       </c>
       <c r="O15" t="n">
-        <v>51937734150</v>
+        <v>71528569790</v>
       </c>
       <c r="P15" t="n">
-        <v>139200</v>
+        <v>40350</v>
       </c>
       <c r="Q15" t="n">
-        <v>57000</v>
+        <v>3320</v>
       </c>
       <c r="R15" t="n">
-        <v>-160000</v>
+        <v>5000</v>
       </c>
       <c r="S15" t="n">
-        <v>-6000</v>
+        <v>15000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>차세대 원자력 및 방산 사업 계약 체결 확정. 대규모 투자 유치 기대감과 함께 공매도 관련 논란.</t>
+          <t>공매도 관련 언급과 함께 체코 원전 수주 기대감, 20000원 안착 및 50000원 목표 제시.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['SMR', '공급 계약', '공매도']</t>
+          <t>['건설', '원전 수주']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,90 +1844,90 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8500</v>
+        <v>17850</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-0.23%</t>
+          <t>'+0.73%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.01</v>
+        <v>-1.68</v>
       </c>
       <c r="E16" t="n">
-        <v>57</v>
+        <v>126</v>
       </c>
       <c r="F16" t="n">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="G16" t="n">
-        <v>178</v>
+        <v>548</v>
       </c>
       <c r="H16" t="n">
-        <v>26.58</v>
+        <v>6.22</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>8520</v>
+        <v>17720</v>
       </c>
       <c r="K16" t="n">
-        <v>8620</v>
+        <v>18230</v>
       </c>
       <c r="L16" t="n">
-        <v>8650</v>
+        <v>18750</v>
       </c>
       <c r="M16" t="n">
-        <v>8410</v>
+        <v>17500</v>
       </c>
       <c r="N16" t="n">
-        <v>26.57</v>
+        <v>7.9</v>
       </c>
       <c r="O16" t="n">
-        <v>10788868100</v>
+        <v>111783990805</v>
       </c>
       <c r="P16" t="n">
-        <v>17950</v>
+        <v>31500</v>
       </c>
       <c r="Q16" t="n">
-        <v>8120</v>
+        <v>1272</v>
       </c>
       <c r="R16" t="n">
-        <v>-212000</v>
+        <v>-359000</v>
       </c>
       <c r="S16" t="n">
-        <v>7000</v>
+        <v>5000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>적자 지속 및 주가 부진에 대한 불만 제기. 반도체 섹터 내 부진한 흐름 지속. 외인 매도세.</t>
+          <t>미국 광통신 섹터 강세에 따른 대한광통신 추가 상승 기대. 악성 개미 물량 털기 및 숏커버 가능성 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['적자', '주가 부진', '외인 매도']</t>
+          <t>['광통신', '미국증시', '숏커버']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,90 +1936,90 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스(Reg.S)</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>21300</v>
+        <v>85200</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-0.93%</t>
+          <t>'-0.12%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.05</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>44</v>
+        <v>167</v>
       </c>
       <c r="F17" t="n">
-        <v>31</v>
+        <v>109</v>
       </c>
       <c r="G17" t="n">
-        <v>129</v>
+        <v>624</v>
       </c>
       <c r="H17" t="n">
-        <v>1.2</v>
+        <v>23.05</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>21500</v>
+        <v>85300</v>
       </c>
       <c r="K17" t="n">
-        <v>21200</v>
+        <v>87000</v>
       </c>
       <c r="L17" t="n">
-        <v>22900</v>
+        <v>87000</v>
       </c>
       <c r="M17" t="n">
-        <v>20850</v>
+        <v>85200</v>
       </c>
       <c r="N17" t="n">
-        <v>1.25</v>
+        <v>23.12</v>
       </c>
       <c r="O17" t="n">
-        <v>37778229875</v>
+        <v>58991525200</v>
       </c>
       <c r="P17" t="n">
-        <v>22900</v>
+        <v>139200</v>
       </c>
       <c r="Q17" t="n">
-        <v>9900</v>
+        <v>57000</v>
       </c>
       <c r="R17" t="n">
-        <v>89000</v>
+        <v>-160000</v>
       </c>
       <c r="S17" t="n">
-        <v>-3000</v>
+        <v>-6000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>글로벌 제약사 (모더나, 머크) 임상 및 투자 소식에 따른 기대감. 반도체 시장 강세와 수급 경쟁 우려.</t>
+          <t>두산에너빌리티의 미국 SMR 추진 확정 및 공급 계약 체결 소식. 공매도 조사 및 심리 게임 언급.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['임상3상', '반도체', '외국인']</t>
+          <t>['SMR', '공급계약', '공매도']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,77 +2028,77 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>950260</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3925</v>
+        <v>8470</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-3.21%</t>
+          <t>'-0.59%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.63</v>
+        <v>0.01</v>
       </c>
       <c r="E18" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="F18" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G18" t="n">
-        <v>204</v>
+        <v>187</v>
       </c>
       <c r="H18" t="n">
-        <v>0.96</v>
+        <v>26.58</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>4055</v>
+        <v>8520</v>
       </c>
       <c r="K18" t="n">
-        <v>4080</v>
+        <v>8620</v>
       </c>
       <c r="L18" t="n">
-        <v>4080</v>
+        <v>8650</v>
       </c>
       <c r="M18" t="n">
-        <v>3850</v>
+        <v>8410</v>
       </c>
       <c r="N18" t="n">
-        <v>0.33</v>
+        <v>26.57</v>
       </c>
       <c r="O18" t="n">
-        <v>6823193575</v>
+        <v>11609408580</v>
       </c>
       <c r="P18" t="n">
-        <v>6480</v>
+        <v>17950</v>
       </c>
       <c r="Q18" t="n">
-        <v>1738</v>
+        <v>8120</v>
       </c>
       <c r="R18" t="n">
-        <v>-44000</v>
+        <v>-212000</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>가상화폐 시장 강세 전망에 따른 기대감. 그러나 명확한 근거 부족 및 주가 하락 추세.</t>
+          <t>실적 부진 및 외국인 매도에 대한 실망감 표출.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['텐베거', '챠트분석', '코인주']</t>
+          <t>['디스플레이', '실적 부진']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,38 +2120,38 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>24300</v>
+        <v>21050</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-3.76%</t>
+          <t>'-2.09%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1.41</v>
+        <v>-0.05</v>
       </c>
       <c r="E19" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="F19" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G19" t="n">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="H19" t="n">
-        <v>1.76</v>
+        <v>1.2</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,51 +2159,51 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>25250</v>
+        <v>21500</v>
       </c>
       <c r="K19" t="n">
-        <v>26150</v>
+        <v>21200</v>
       </c>
       <c r="L19" t="n">
-        <v>26600</v>
+        <v>22900</v>
       </c>
       <c r="M19" t="n">
-        <v>24050</v>
+        <v>20850</v>
       </c>
       <c r="N19" t="n">
-        <v>0.35</v>
+        <v>1.25</v>
       </c>
       <c r="O19" t="n">
-        <v>77156634425</v>
+        <v>38723087950</v>
       </c>
       <c r="P19" t="n">
-        <v>39350</v>
+        <v>22900</v>
       </c>
       <c r="Q19" t="n">
-        <v>8200</v>
+        <v>9900</v>
       </c>
       <c r="R19" t="n">
-        <v>-10000</v>
+        <v>89000</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>코스닥 역사 쓸 종목으로 평가되며 연상 기대감. 프로그램 매집 확인 및 매물 소화 중.</t>
+          <t>모더나 및 미국 반도체 주식 폭등에 따른 인제니아테라퓨틱스 수급 기대. 머크의 임상 3상 투자 소식 및 외인 매수세 유입.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['연상', '매물 소화', '프로그램 매집']</t>
+          <t>['모더나', '반도체', '임상3상']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,97 +2212,281 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>950260</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10520</v>
+        <v>24450</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-4.88%</t>
+          <t>'-3.17%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.4</v>
+        <v>1.41</v>
       </c>
       <c r="E20" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F20" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G20" t="n">
-        <v>155</v>
+        <v>112</v>
       </c>
       <c r="H20" t="n">
-        <v>17.89</v>
+        <v>1.76</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>11060</v>
+        <v>25250</v>
       </c>
       <c r="K20" t="n">
-        <v>10570</v>
+        <v>26150</v>
       </c>
       <c r="L20" t="n">
-        <v>10815</v>
+        <v>26600</v>
       </c>
       <c r="M20" t="n">
-        <v>10060</v>
+        <v>24000</v>
       </c>
       <c r="N20" t="n">
-        <v>18.29</v>
+        <v>0.35</v>
       </c>
       <c r="O20" t="n">
-        <v>26656375000</v>
+        <v>79973660500</v>
       </c>
       <c r="P20" t="n">
-        <v>22450</v>
+        <v>39350</v>
       </c>
       <c r="Q20" t="n">
-        <v>1760</v>
+        <v>8200</v>
       </c>
       <c r="R20" t="n">
-        <v>3000</v>
+        <v>-10000</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>투자 경고 종목 지정 및 주가 하락세 지속. 미래 먹거리 관련 언급 있으나 실질적 근거 부족.</t>
+          <t>스카이랩스의 기술력 및 협업 가능성은 긍정적이나, 단기 급등 후 차익 실현 매물 출회 및 하락세 조짐. 주포 움직임 주목.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['투자경고', '주가 하락', '미래 먹거리']</t>
+          <t>['기술력', '협업', '차익실현']</t>
         </is>
       </c>
       <c r="X20" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>386380</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>미투온</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>3905</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>'-3.70%</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E21" t="n">
+        <v>49</v>
+      </c>
+      <c r="F21" t="n">
+        <v>38</v>
+      </c>
+      <c r="G21" t="n">
+        <v>214</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>4055</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4080</v>
+      </c>
+      <c r="L21" t="n">
+        <v>4080</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3850</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="O21" t="n">
+        <v>7177748830</v>
+      </c>
+      <c r="P21" t="n">
+        <v>6480</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1738</v>
+      </c>
+      <c r="R21" t="n">
+        <v>-44000</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>비트코인 회복 소식에도 불구하고 미투온 차트상 하락세 지속 및 신용 물량 털어내기 가능성. 인수 및 스테이블 코인 관련 불확실성.</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>['비트코인', '차트분석', '신용물량']</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>201490</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>광전자</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>10560</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>'-4.52%</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E22" t="n">
+        <v>66</v>
+      </c>
+      <c r="F22" t="n">
+        <v>47</v>
+      </c>
+      <c r="G22" t="n">
+        <v>165</v>
+      </c>
+      <c r="H22" t="n">
+        <v>17.89</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>11060</v>
+      </c>
+      <c r="K22" t="n">
+        <v>10570</v>
+      </c>
+      <c r="L22" t="n">
+        <v>10815</v>
+      </c>
+      <c r="M22" t="n">
+        <v>10060</v>
+      </c>
+      <c r="N22" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="O22" t="n">
+        <v>28382381890</v>
+      </c>
+      <c r="P22" t="n">
+        <v>22450</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1760</v>
+      </c>
+      <c r="R22" t="n">
+        <v>3000</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>투자경고 종목 지정 및 주가 하락에 대한 불만 표출.</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>['투자경고', '주가 하락']</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
         <v>7</v>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>017900</t>
         </is>

--- a/data/trending_integrated_20260922_10.xlsx
+++ b/data/trending_integrated_20260922_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z22"/>
+  <dimension ref="A1:Z24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>0.04</v>
       </c>
       <c r="E2" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G2" t="n">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="H2" t="n">
         <v>0.6899999999999999</v>
@@ -610,7 +610,7 @@
         <v>0.65</v>
       </c>
       <c r="O2" t="n">
-        <v>34875939090</v>
+        <v>34904284440</v>
       </c>
       <c r="P2" t="n">
         <v>65300</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>노타의 국산 NPU 기반 휴머노이드 개발 착수 및 AI 반도체 파트너십 부각. 로봇 속도 3배 초가속 관련 기술력 강조.</t>
+          <t>국산 NPU 기반 휴머노이드 개발 착수 뉴스 및 인텔 협력사 관련 호재. AI 반도체 파트너십 부각.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['NPU', '휴머노이드', 'AI반도체']</t>
+          <t>['NPU', '휴머노이드', 'AI 반도체']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>-0.22</v>
       </c>
       <c r="E3" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G3" t="n">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H3" t="n">
         <v>0.48</v>
@@ -702,7 +702,7 @@
         <v>0.7</v>
       </c>
       <c r="O3" t="n">
-        <v>5249119339</v>
+        <v>5262009519</v>
       </c>
       <c r="P3" t="n">
         <v>4760</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>66100</v>
+        <v>66800</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+26.39%</t>
+          <t>'+27.72%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F4" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G4" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H4" t="n">
         <v>6.87</v>
@@ -794,7 +794,7 @@
         <v>6.88</v>
       </c>
       <c r="O4" t="n">
-        <v>111853979050</v>
+        <v>114185983950</v>
       </c>
       <c r="P4" t="n">
         <v>148300</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>상한가 기록 및 27% 급등에 대한 환호, 6만원 위 매도 의견 및 반도체 장기 투자 부정론 언급.</t>
+          <t>반도체 섹터 강세 속 주가 급등 및 키맞추기 기대. 6만원 이상 매도 의견 및 단기 상승 후 하락 가능성 경고.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['반도체', '급등주']</t>
+          <t>['반도체', '급등', '키맞추기']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>114200</v>
+        <v>114800</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+12.07%</t>
+          <t>'+12.66%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.12</v>
       </c>
       <c r="E5" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F5" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G5" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H5" t="n">
         <v>18.2</v>
@@ -886,7 +886,7 @@
         <v>18.32</v>
       </c>
       <c r="O5" t="n">
-        <v>224967457300</v>
+        <v>232964312950</v>
       </c>
       <c r="P5" t="n">
         <v>198000</v>
@@ -902,7 +902,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>SK하이닉스 GDDR7 공급망 수혜 기대감 및 110,000원대 허리 구간 언급.</t>
+          <t>SK하이닉스 GDDR7 기판 공급망 확대 수혜 기대감. 주가 변동성 및 개인 투자자 보유 의견.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,7 +911,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['PCB', '반도체 소재']</t>
+          <t>['GDDR7', '기판', '수혜']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,83 +931,83 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>우리기술투자</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6340</v>
+        <v>32100</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+8.19%</t>
+          <t>'+8.08%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.19</v>
+        <v>-0.62</v>
       </c>
       <c r="E6" t="n">
+        <v>78</v>
+      </c>
+      <c r="F6" t="n">
         <v>57</v>
       </c>
-      <c r="F6" t="n">
-        <v>43</v>
-      </c>
       <c r="G6" t="n">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>11.3</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>5860</v>
+        <v>29700</v>
       </c>
       <c r="K6" t="n">
-        <v>6200</v>
+        <v>30500</v>
       </c>
       <c r="L6" t="n">
-        <v>6610</v>
+        <v>33450</v>
       </c>
       <c r="M6" t="n">
-        <v>6150</v>
+        <v>30000</v>
       </c>
       <c r="N6" t="n">
-        <v>0.19</v>
+        <v>11.92</v>
       </c>
       <c r="O6" t="n">
-        <v>46305333975</v>
+        <v>202324553200</v>
       </c>
       <c r="P6" t="n">
-        <v>13140</v>
+        <v>75900</v>
       </c>
       <c r="Q6" t="n">
-        <v>3725</v>
+        <v>15000</v>
       </c>
       <c r="R6" t="n">
-        <v>168000</v>
+        <v>351000</v>
       </c>
       <c r="S6" t="n">
-        <v>23000</v>
+        <v>6000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>비트코인 급등과 가상화폐 테마의 반란으로 인한 우리기술투자의 강세 전망. 공개매수 진행 및 외인 매수세 유입 기대.</t>
+          <t>신고점 돌파한 가온전선과 비교되며 주가 상승에 대한 기대감과 하락 우려가 혼재. 단기 3만 5천원 가능성 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['비트코인', '가상화폐', '공개매수']</t>
+          <t>['거래량', '상승', '목표가']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>041190</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>우리기술투자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32100</v>
+        <v>6310</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+8.08%</t>
+          <t>'+7.68%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.62</v>
+        <v>-0.19</v>
       </c>
       <c r="E7" t="n">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="F7" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G7" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="H7" t="n">
-        <v>11.3</v>
+        <v>0</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>29700</v>
+        <v>5860</v>
       </c>
       <c r="K7" t="n">
-        <v>30500</v>
+        <v>6200</v>
       </c>
       <c r="L7" t="n">
-        <v>33450</v>
+        <v>6610</v>
       </c>
       <c r="M7" t="n">
-        <v>30000</v>
+        <v>6150</v>
       </c>
       <c r="N7" t="n">
-        <v>11.92</v>
+        <v>0.19</v>
       </c>
       <c r="O7" t="n">
-        <v>198109142550</v>
+        <v>48156608300</v>
       </c>
       <c r="P7" t="n">
-        <v>75900</v>
+        <v>13140</v>
       </c>
       <c r="Q7" t="n">
-        <v>15000</v>
+        <v>3725</v>
       </c>
       <c r="R7" t="n">
-        <v>351000</v>
+        <v>168000</v>
       </c>
       <c r="S7" t="n">
-        <v>6000</v>
+        <v>23000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>가온전선과의 비교 속에서 700원 벽 돌파 실패 및 단기 목표가 언급.</t>
+          <t>비트코인 급등 및 가상화폐 테마 확산에 따른 우리기술투자 상승 기대. 공개매수 및 공매도 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.6</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['전선주', '주가 전망']</t>
+          <t>['비트코인', '가상화폐', '공개매수']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>041190</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6560</v>
+        <v>6660</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+3.96%</t>
+          <t>'+5.55%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.09</v>
       </c>
       <c r="E8" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G8" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="H8" t="n">
         <v>4.86</v>
@@ -1162,7 +1162,7 @@
         <v>4.95</v>
       </c>
       <c r="O8" t="n">
-        <v>43924102880</v>
+        <v>44547935760</v>
       </c>
       <c r="P8" t="n">
         <v>11760</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>KBI메탈의 매집 및 시총 가벼움은 긍정적이나, 외인 물량 폭탄 매도 및 추격 매수 경고. 전쟁 확산 가능성 언급.</t>
+          <t>기초 체력 강화 및 저평가 인식 속 외인 매도세 관찰. 추석 이후 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['매집', '외인매도', '전쟁주']</t>
+          <t>['체력 강화', '외인 매도', '추석']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14050</v>
+        <v>30400</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.77%</t>
+          <t>'+5.37%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.34</v>
+        <v>-0.04</v>
       </c>
       <c r="E9" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F9" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G9" t="n">
-        <v>69</v>
+        <v>137</v>
       </c>
       <c r="H9" t="n">
-        <v>3.34</v>
+        <v>51.73</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>13540</v>
+        <v>28850</v>
       </c>
       <c r="K9" t="n">
-        <v>13870</v>
+        <v>29250</v>
       </c>
       <c r="L9" t="n">
-        <v>14650</v>
+        <v>30450</v>
       </c>
       <c r="M9" t="n">
-        <v>13740</v>
+        <v>29150</v>
       </c>
       <c r="N9" t="n">
-        <v>3.68</v>
+        <v>25.79</v>
       </c>
       <c r="O9" t="n">
-        <v>77795417365</v>
+        <v>47842061750</v>
       </c>
       <c r="P9" t="n">
-        <v>20300</v>
+        <v>31200</v>
       </c>
       <c r="Q9" t="n">
-        <v>2885</v>
+        <v>21000</v>
       </c>
       <c r="R9" t="n">
-        <v>236000</v>
+        <v>125000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>38000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>AI 시대 전력망 중요성 언급 및 대한전선과의 비교 속에서 15000원대 탈출 목표 제시.</t>
+          <t>국제유가 및 환율 하락 속 주가 상승 기대. JP모간 순매수 확인 및 방산, 드론, 무인기 등 연관 사업 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['전력망', '테마주']</t>
+          <t>['국제유가', '환율', 'JP모간']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>330500</v>
+        <v>331000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.77%</t>
+          <t>'+3.92%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.4</v>
       </c>
       <c r="E10" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G10" t="n">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="H10" t="n">
         <v>3.22</v>
@@ -1346,7 +1346,7 @@
         <v>3.62</v>
       </c>
       <c r="O10" t="n">
-        <v>92750109750</v>
+        <v>93872003250</v>
       </c>
       <c r="P10" t="n">
         <v>635000</v>
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1918000</v>
+        <v>14070</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.68%</t>
+          <t>'+3.91%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.06</v>
+        <v>-0.34</v>
       </c>
       <c r="E11" t="n">
-        <v>730</v>
+        <v>42</v>
       </c>
       <c r="F11" t="n">
-        <v>440</v>
+        <v>27</v>
       </c>
       <c r="G11" t="n">
-        <v>3350</v>
+        <v>72</v>
       </c>
       <c r="H11" t="n">
-        <v>50.17</v>
+        <v>3.34</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,51 +1423,51 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1868000</v>
+        <v>13540</v>
       </c>
       <c r="K11" t="n">
-        <v>1909000</v>
+        <v>13870</v>
       </c>
       <c r="L11" t="n">
-        <v>1935000</v>
+        <v>14650</v>
       </c>
       <c r="M11" t="n">
-        <v>1904000</v>
+        <v>13740</v>
       </c>
       <c r="N11" t="n">
-        <v>50.23</v>
+        <v>3.68</v>
       </c>
       <c r="O11" t="n">
-        <v>1689036804500</v>
+        <v>78880188340</v>
       </c>
       <c r="P11" t="n">
-        <v>2987000</v>
+        <v>20300</v>
       </c>
       <c r="Q11" t="n">
-        <v>333000</v>
+        <v>2885</v>
       </c>
       <c r="R11" t="n">
-        <v>85000</v>
+        <v>236000</v>
       </c>
       <c r="S11" t="n">
-        <v>55000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>AI 반도체 주 강세 및 뉴욕 증시 급등에 따른 SK하이닉스 주가 상승 기대.</t>
+          <t>AI 시대 전력망 중요성 및 모건스탠리 분석 언급. 대한전선과의 비교 및 14000원대 돌파 시도, 연간 영업이익 300억 초과 기대.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['AI', '반도체', '뉴욕증시']</t>
+          <t>['AI', '전력망', '영업이익']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>76</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,90 +1476,90 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>006340</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>SFA반도체</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13280</v>
+        <v>10890</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.47%</t>
+          <t>'+3.22%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="E12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G12" t="n">
-        <v>189</v>
+        <v>112</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>12960</v>
+        <v>10550</v>
       </c>
       <c r="K12" t="n">
-        <v>13500</v>
+        <v>10730</v>
       </c>
       <c r="L12" t="n">
-        <v>14190</v>
+        <v>11160</v>
       </c>
       <c r="M12" t="n">
-        <v>13270</v>
+        <v>10300</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="O12" t="n">
-        <v>17464125000</v>
+        <v>96448474165</v>
       </c>
       <c r="P12" t="n">
-        <v>19380</v>
+        <v>11640</v>
       </c>
       <c r="Q12" t="n">
-        <v>3200</v>
+        <v>3735</v>
       </c>
       <c r="R12" t="n">
-        <v>-40000</v>
+        <v>-140000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>광주 삼성전자 공장 착공 소식 및 호남 지역 호황 언급, 15000원대 물려있는 투자자들에 대한 우려 제기.</t>
+          <t>외인 매도세 속 반등 기대감 및 공매도 논란. 반도체 후공정 테마 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['건설', '반도체 공장']</t>
+          <t>['반도체', '후공정', '공매도']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>036540</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SFA반도체</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10810</v>
+        <v>13320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.46%</t>
+          <t>'+2.78%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F13" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G13" t="n">
-        <v>96</v>
+        <v>209</v>
       </c>
       <c r="H13" t="n">
-        <v>9.609999999999999</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>10550</v>
+        <v>12960</v>
       </c>
       <c r="K13" t="n">
-        <v>10730</v>
+        <v>13500</v>
       </c>
       <c r="L13" t="n">
-        <v>11160</v>
+        <v>14190</v>
       </c>
       <c r="M13" t="n">
-        <v>10300</v>
+        <v>13270</v>
       </c>
       <c r="N13" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>90001210565</v>
+        <v>17772662450</v>
       </c>
       <c r="P13" t="n">
-        <v>11640</v>
+        <v>19380</v>
       </c>
       <c r="Q13" t="n">
-        <v>3735</v>
+        <v>3200</v>
       </c>
       <c r="R13" t="n">
-        <v>-140000</v>
+        <v>-40000</v>
       </c>
       <c r="S13" t="n">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>반도체 조정 국면 속에서 2주간의 조정 이후 반등 기대감 언급.</t>
+          <t>광주 삼성전자 공장 착공 관련 호재 언급. 매출액 증가 및 주포 활동에 대한 기대감과 주의 의견.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['반도체', '조정']</t>
+          <t>['삼성전자', '공장 착공', '매출액']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>036540</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>279500</v>
+        <v>1918000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.01%</t>
+          <t>'+2.68%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.1</v>
+        <v>-0.06</v>
       </c>
       <c r="E14" t="n">
-        <v>800</v>
+        <v>755</v>
       </c>
       <c r="F14" t="n">
-        <v>493</v>
+        <v>459</v>
       </c>
       <c r="G14" t="n">
-        <v>3924</v>
+        <v>3412</v>
       </c>
       <c r="H14" t="n">
-        <v>46.56</v>
+        <v>50.17</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>274000</v>
+        <v>1868000</v>
       </c>
       <c r="K14" t="n">
-        <v>283000</v>
+        <v>1909000</v>
       </c>
       <c r="L14" t="n">
-        <v>283500</v>
+        <v>1935000</v>
       </c>
       <c r="M14" t="n">
-        <v>279000</v>
+        <v>1904000</v>
       </c>
       <c r="N14" t="n">
-        <v>46.46</v>
+        <v>50.23</v>
       </c>
       <c r="O14" t="n">
-        <v>1330659921250</v>
+        <v>1794612656000</v>
       </c>
       <c r="P14" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q14" t="n">
-        <v>81100</v>
+        <v>333000</v>
       </c>
       <c r="R14" t="n">
-        <v>26000</v>
+        <v>85000</v>
       </c>
       <c r="S14" t="n">
-        <v>42000</v>
+        <v>55000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>3분기 역대급 실적 기대감 속 30만원 돌파 및 미 증시 폭등 영향 언급.</t>
+          <t>AI 반도체 주 강세 및 뉴욕 증시 급등에 따른 SK하이닉스 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['반도체', '실적 전망']</t>
+          <t>['AI', '반도체', '뉴욕증시']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18610</v>
+        <v>212500</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+1.75%</t>
+          <t>'+2.16%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.27</v>
+        <v>0.06</v>
       </c>
       <c r="E15" t="n">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="F15" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="G15" t="n">
-        <v>331</v>
+        <v>189</v>
       </c>
       <c r="H15" t="n">
-        <v>10.47</v>
+        <v>75.5</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>18290</v>
+        <v>208000</v>
       </c>
       <c r="K15" t="n">
-        <v>18830</v>
+        <v>215000</v>
       </c>
       <c r="L15" t="n">
-        <v>19540</v>
+        <v>215000</v>
       </c>
       <c r="M15" t="n">
-        <v>18560</v>
+        <v>211000</v>
       </c>
       <c r="N15" t="n">
-        <v>10.74</v>
+        <v>75.44</v>
       </c>
       <c r="O15" t="n">
-        <v>71528569790</v>
+        <v>379737276250</v>
       </c>
       <c r="P15" t="n">
-        <v>40350</v>
+        <v>243500</v>
       </c>
       <c r="Q15" t="n">
-        <v>3320</v>
+        <v>64700</v>
       </c>
       <c r="R15" t="n">
-        <v>5000</v>
+        <v>-376000</v>
       </c>
       <c r="S15" t="n">
-        <v>15000</v>
+        <v>12000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>공매도 관련 언급과 함께 체코 원전 수주 기대감, 20000원 안착 및 50000원 목표 제시.</t>
+          <t>배당 기대감 속에 주가 상승 및 21만원 돌파 가능성 언급. 자사주 매입 및 외국인 순매수 시 재진입 고려.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['건설', '원전 수주']</t>
+          <t>['배당', '자사주 매입', '우선주']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,90 +1844,90 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17850</v>
+        <v>279500</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+0.73%</t>
+          <t>'+2.01%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-1.68</v>
+        <v>0.1</v>
       </c>
       <c r="E16" t="n">
-        <v>126</v>
+        <v>800</v>
       </c>
       <c r="F16" t="n">
-        <v>79</v>
+        <v>496</v>
       </c>
       <c r="G16" t="n">
-        <v>548</v>
+        <v>3514</v>
       </c>
       <c r="H16" t="n">
-        <v>6.22</v>
+        <v>46.56</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>17720</v>
+        <v>274000</v>
       </c>
       <c r="K16" t="n">
-        <v>18230</v>
+        <v>283000</v>
       </c>
       <c r="L16" t="n">
-        <v>18750</v>
+        <v>283500</v>
       </c>
       <c r="M16" t="n">
-        <v>17500</v>
+        <v>279000</v>
       </c>
       <c r="N16" t="n">
-        <v>7.9</v>
+        <v>46.46</v>
       </c>
       <c r="O16" t="n">
-        <v>111783990805</v>
+        <v>1414664226750</v>
       </c>
       <c r="P16" t="n">
-        <v>31500</v>
+        <v>374500</v>
       </c>
       <c r="Q16" t="n">
-        <v>1272</v>
+        <v>81100</v>
       </c>
       <c r="R16" t="n">
-        <v>-359000</v>
+        <v>26000</v>
       </c>
       <c r="S16" t="n">
-        <v>5000</v>
+        <v>42000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>미국 광통신 섹터 강세에 따른 대한광통신 추가 상승 기대. 악성 개미 물량 털기 및 숏커버 가능성 언급.</t>
+          <t>3분기 역대급 실적 기대감 속 30만 돌파 및 추가 상승 전망. 미국 증시 반도체 대폭등 영향 및 개인 매수세 유입.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['광통신', '미국증시', '숏커버']</t>
+          <t>['3분기 실적', '반도체', '상승']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>20</v>
+        <v>111</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>85200</v>
+        <v>18590</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-0.12%</t>
+          <t>'+1.64%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.27</v>
       </c>
       <c r="E17" t="n">
-        <v>167</v>
+        <v>85</v>
       </c>
       <c r="F17" t="n">
-        <v>109</v>
+        <v>50</v>
       </c>
       <c r="G17" t="n">
-        <v>624</v>
+        <v>346</v>
       </c>
       <c r="H17" t="n">
-        <v>23.05</v>
+        <v>10.47</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,51 +1975,51 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>85300</v>
+        <v>18290</v>
       </c>
       <c r="K17" t="n">
-        <v>87000</v>
+        <v>18830</v>
       </c>
       <c r="L17" t="n">
-        <v>87000</v>
+        <v>19540</v>
       </c>
       <c r="M17" t="n">
-        <v>85200</v>
+        <v>18550</v>
       </c>
       <c r="N17" t="n">
-        <v>23.12</v>
+        <v>10.74</v>
       </c>
       <c r="O17" t="n">
-        <v>58991525200</v>
+        <v>73558019390</v>
       </c>
       <c r="P17" t="n">
-        <v>139200</v>
+        <v>40350</v>
       </c>
       <c r="Q17" t="n">
-        <v>57000</v>
+        <v>3320</v>
       </c>
       <c r="R17" t="n">
-        <v>-160000</v>
+        <v>5000</v>
       </c>
       <c r="S17" t="n">
-        <v>-6000</v>
+        <v>15000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>두산에너빌리티의 미국 SMR 추진 확정 및 공급 계약 체결 소식. 공매도 조사 및 심리 게임 언급.</t>
+          <t>미국 증시 폭등 속 공매도 관련 불만 제기. 체코 원전 수주 기대감 및 연기금 순매수 확인, 10월 전고점 돌파 전망.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['SMR', '공급계약', '공매도']</t>
+          <t>['공매도', '체코 원전', '연기금']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,90 +2028,90 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>8470</v>
+        <v>17820</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-0.59%</t>
+          <t>'+0.56%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.01</v>
+        <v>-1.68</v>
       </c>
       <c r="E18" t="n">
-        <v>63</v>
+        <v>128</v>
       </c>
       <c r="F18" t="n">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="G18" t="n">
-        <v>187</v>
+        <v>558</v>
       </c>
       <c r="H18" t="n">
-        <v>26.58</v>
+        <v>6.22</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>8520</v>
+        <v>17720</v>
       </c>
       <c r="K18" t="n">
-        <v>8620</v>
+        <v>18230</v>
       </c>
       <c r="L18" t="n">
-        <v>8650</v>
+        <v>18750</v>
       </c>
       <c r="M18" t="n">
-        <v>8410</v>
+        <v>17500</v>
       </c>
       <c r="N18" t="n">
-        <v>26.57</v>
+        <v>7.9</v>
       </c>
       <c r="O18" t="n">
-        <v>11609408580</v>
+        <v>114353753055</v>
       </c>
       <c r="P18" t="n">
-        <v>17950</v>
+        <v>31500</v>
       </c>
       <c r="Q18" t="n">
-        <v>8120</v>
+        <v>1272</v>
       </c>
       <c r="R18" t="n">
-        <v>-212000</v>
+        <v>-359000</v>
       </c>
       <c r="S18" t="n">
-        <v>7000</v>
+        <v>5000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>실적 부진 및 외국인 매도에 대한 실망감 표출.</t>
+          <t>미국 광통신 섹터 강세에 따른 대한광통신 추가 상승 기대. 악성 개미 물량 털기 및 숏커버 가능성 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['디스플레이', '실적 부진']</t>
+          <t>['광통신', '미국증시', '숏커버']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,90 +2120,90 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스(Reg.S)</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>21050</v>
+        <v>85200</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-2.09%</t>
+          <t>'-0.12%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.05</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>49</v>
+        <v>189</v>
       </c>
       <c r="F19" t="n">
-        <v>33</v>
+        <v>125</v>
       </c>
       <c r="G19" t="n">
-        <v>132</v>
+        <v>705</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2</v>
+        <v>23.05</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>21500</v>
+        <v>85300</v>
       </c>
       <c r="K19" t="n">
-        <v>21200</v>
+        <v>87000</v>
       </c>
       <c r="L19" t="n">
-        <v>22900</v>
+        <v>87000</v>
       </c>
       <c r="M19" t="n">
-        <v>20850</v>
+        <v>85200</v>
       </c>
       <c r="N19" t="n">
-        <v>1.25</v>
+        <v>23.12</v>
       </c>
       <c r="O19" t="n">
-        <v>38723087950</v>
+        <v>62302379900</v>
       </c>
       <c r="P19" t="n">
-        <v>22900</v>
+        <v>139200</v>
       </c>
       <c r="Q19" t="n">
-        <v>9900</v>
+        <v>57000</v>
       </c>
       <c r="R19" t="n">
-        <v>89000</v>
+        <v>-160000</v>
       </c>
       <c r="S19" t="n">
-        <v>-3000</v>
+        <v>-6000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>모더나 및 미국 반도체 주식 폭등에 따른 인제니아테라퓨틱스 수급 기대. 머크의 임상 3상 투자 소식 및 외인 매수세 유입.</t>
+          <t>SMR 사업 추진 및 공급 계약 체결 확정. 대미 투자 관련 긍정적 뉴스 언급.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['모더나', '반도체', '임상3상']</t>
+          <t>['SMR', '공급 계약', '대미 투자']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,90 +2212,90 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>950260</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>24450</v>
+        <v>8460</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-3.17%</t>
+          <t>'-0.70%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1.41</v>
+        <v>0.01</v>
       </c>
       <c r="E20" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="F20" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G20" t="n">
-        <v>112</v>
+        <v>216</v>
       </c>
       <c r="H20" t="n">
-        <v>1.76</v>
+        <v>26.58</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>25250</v>
+        <v>8520</v>
       </c>
       <c r="K20" t="n">
-        <v>26150</v>
+        <v>8620</v>
       </c>
       <c r="L20" t="n">
-        <v>26600</v>
+        <v>8650</v>
       </c>
       <c r="M20" t="n">
-        <v>24000</v>
+        <v>8410</v>
       </c>
       <c r="N20" t="n">
-        <v>0.35</v>
+        <v>26.57</v>
       </c>
       <c r="O20" t="n">
-        <v>79973660500</v>
+        <v>11976418790</v>
       </c>
       <c r="P20" t="n">
-        <v>39350</v>
+        <v>17950</v>
       </c>
       <c r="Q20" t="n">
-        <v>8200</v>
+        <v>8120</v>
       </c>
       <c r="R20" t="n">
-        <v>-10000</v>
+        <v>-212000</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>스카이랩스의 기술력 및 협업 가능성은 긍정적이나, 단기 급등 후 차익 실현 매물 출회 및 하락세 조짐. 주포 움직임 주목.</t>
+          <t>주가 부진 및 무능한 경영에 대한 불만 표출. 외국인 순매도 지속 및 장기 소외, 비전 부재 지적.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['기술력', '협업', '차익실현']</t>
+          <t>['무능', '외국인', '소외']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,38 +2304,38 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3905</v>
+        <v>21100</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-3.70%</t>
+          <t>'-1.86%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.63</v>
+        <v>-0.05</v>
       </c>
       <c r="E21" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F21" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G21" t="n">
-        <v>214</v>
+        <v>142</v>
       </c>
       <c r="H21" t="n">
-        <v>0.96</v>
+        <v>1.2</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,51 +2343,51 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>4055</v>
+        <v>21500</v>
       </c>
       <c r="K21" t="n">
-        <v>4080</v>
+        <v>21200</v>
       </c>
       <c r="L21" t="n">
-        <v>4080</v>
+        <v>22900</v>
       </c>
       <c r="M21" t="n">
-        <v>3850</v>
+        <v>20850</v>
       </c>
       <c r="N21" t="n">
-        <v>0.33</v>
+        <v>1.25</v>
       </c>
       <c r="O21" t="n">
-        <v>7177748830</v>
+        <v>39485811400</v>
       </c>
       <c r="P21" t="n">
-        <v>6480</v>
+        <v>22900</v>
       </c>
       <c r="Q21" t="n">
-        <v>1738</v>
+        <v>9900</v>
       </c>
       <c r="R21" t="n">
-        <v>-44000</v>
+        <v>89000</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>비트코인 회복 소식에도 불구하고 미투온 차트상 하락세 지속 및 신용 물량 털어내기 가능성. 인수 및 스테이블 코인 관련 불확실성.</t>
+          <t>모더나 폭등 및 머크 임상 3상 투자 소식에 따른 주가 강세 기대. 외국인 매수세 유입.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['비트코인', '차트분석', '신용물량']</t>
+          <t>['모더나', '임상 3상', '외국인']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,99 +2396,283 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>950260</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10560</v>
+        <v>3905</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-4.52%</t>
+          <t>'-3.70%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-0.4</v>
+        <v>0.63</v>
       </c>
       <c r="E22" t="n">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="F22" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="G22" t="n">
-        <v>165</v>
+        <v>215</v>
       </c>
       <c r="H22" t="n">
-        <v>17.89</v>
+        <v>0.96</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>11060</v>
+        <v>4055</v>
       </c>
       <c r="K22" t="n">
-        <v>10570</v>
+        <v>4080</v>
       </c>
       <c r="L22" t="n">
-        <v>10815</v>
+        <v>4080</v>
       </c>
       <c r="M22" t="n">
-        <v>10060</v>
+        <v>3850</v>
       </c>
       <c r="N22" t="n">
-        <v>18.29</v>
+        <v>0.33</v>
       </c>
       <c r="O22" t="n">
-        <v>28382381890</v>
+        <v>7353413060</v>
       </c>
       <c r="P22" t="n">
-        <v>22450</v>
+        <v>6480</v>
       </c>
       <c r="Q22" t="n">
-        <v>1760</v>
+        <v>1738</v>
       </c>
       <c r="R22" t="n">
-        <v>3000</v>
+        <v>-44000</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>투자경고 종목 지정 및 주가 하락에 대한 불만 표출.</t>
+          <t>비트코인 회복 소식에도 불구하고 미투온 차트상 하락세 지속 및 신용 물량 털어내기 가능성. 인수 및 스테이블 코인 관련 불확실성.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>['비트코인', '차트분석', '신용물량']</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>201490</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>광전자</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>10610</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>'-4.07%</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E23" t="n">
+        <v>68</v>
+      </c>
+      <c r="F23" t="n">
+        <v>49</v>
+      </c>
+      <c r="G23" t="n">
+        <v>165</v>
+      </c>
+      <c r="H23" t="n">
+        <v>17.89</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>11060</v>
+      </c>
+      <c r="K23" t="n">
+        <v>10570</v>
+      </c>
+      <c r="L23" t="n">
+        <v>10815</v>
+      </c>
+      <c r="M23" t="n">
+        <v>10060</v>
+      </c>
+      <c r="N23" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="O23" t="n">
+        <v>29516966690</v>
+      </c>
+      <c r="P23" t="n">
+        <v>22450</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1760</v>
+      </c>
+      <c r="R23" t="n">
+        <v>3000</v>
+      </c>
+      <c r="S23" t="n">
         <v>0</v>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>투자경고 종목 지정 및 주가 하락에 대한 불만 표출.</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="inlineStr">
         <is>
           <t>['투자경고', '주가 하락']</t>
         </is>
       </c>
-      <c r="X22" t="n">
+      <c r="X23" t="n">
         <v>7</v>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>017900</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>스카이랩스</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>23850</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>'-5.54%</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="E24" t="n">
+        <v>66</v>
+      </c>
+      <c r="F24" t="n">
+        <v>43</v>
+      </c>
+      <c r="G24" t="n">
+        <v>128</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>25250</v>
+      </c>
+      <c r="K24" t="n">
+        <v>26150</v>
+      </c>
+      <c r="L24" t="n">
+        <v>26600</v>
+      </c>
+      <c r="M24" t="n">
+        <v>23800</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O24" t="n">
+        <v>84588701925</v>
+      </c>
+      <c r="P24" t="n">
+        <v>39350</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>8200</v>
+      </c>
+      <c r="R24" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>신규 상장 후 변동성, 연상 기대감 대비 하락세. 주포 활동 및 쫄보 매도 언급.</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>['신규 상장', '주포', '변동성']</t>
+        </is>
+      </c>
+      <c r="X24" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>386380</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260922_10.xlsx
+++ b/data/trending_integrated_20260922_10.xlsx
@@ -578,13 +578,13 @@
         <v>0.04</v>
       </c>
       <c r="E2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F2" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G2" t="n">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="H2" t="n">
         <v>0.6899999999999999</v>
@@ -610,7 +610,7 @@
         <v>0.65</v>
       </c>
       <c r="O2" t="n">
-        <v>34904284440</v>
+        <v>34907734590</v>
       </c>
       <c r="P2" t="n">
         <v>65300</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>국산 NPU 기반 휴머노이드 개발 착수 뉴스 및 인텔 협력사 관련 호재. AI 반도체 파트너십 부각.</t>
+          <t>국산 NPU 기반 휴머노이드 개발 착수 및 AI 반도체 파트너십 기대. 로봇 속도 초가속 관련 긍정적 분석.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['NPU', '휴머노이드', 'AI 반도체']</t>
+          <t>['NPU', '휴머노이드', 'AI반도체']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>-0.22</v>
       </c>
       <c r="E3" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G3" t="n">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="H3" t="n">
         <v>0.48</v>
@@ -702,7 +702,7 @@
         <v>0.7</v>
       </c>
       <c r="O3" t="n">
-        <v>5262009519</v>
+        <v>5266455304</v>
       </c>
       <c r="P3" t="n">
         <v>4760</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>악재 해소 및 K-바이오 섹터 상승 기대감. 기관 투자자 지분 확보 및 공매도 상환 압박 분석.</t>
+          <t>악재 해소 및 기관 투자자 주목. 휴니버스 글로벌, 항암 백신 관련 긍정적 분석 및 공매도 상환가격 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['K-바이오', '기관 투자자', '공매도']</t>
+          <t>['항암백신', '공매도', '휴니버스']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,21 +751,21 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>66800</v>
+        <v>67200</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+27.72%</t>
+          <t>'+28.49%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F4" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G4" t="n">
         <v>85</v>
@@ -794,7 +794,7 @@
         <v>6.88</v>
       </c>
       <c r="O4" t="n">
-        <v>114185983950</v>
+        <v>117114580150</v>
       </c>
       <c r="P4" t="n">
         <v>148300</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>114800</v>
+        <v>115850</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+12.66%</t>
+          <t>'+13.69%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.12</v>
       </c>
       <c r="E5" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F5" t="n">
         <v>41</v>
       </c>
       <c r="G5" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="H5" t="n">
         <v>18.2</v>
@@ -886,7 +886,7 @@
         <v>18.32</v>
       </c>
       <c r="O5" t="n">
-        <v>232964312950</v>
+        <v>239094812650</v>
       </c>
       <c r="P5" t="n">
         <v>198000</v>
@@ -902,12 +902,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>SK하이닉스 GDDR7 기판 공급망 확대 수혜 기대감. 주가 변동성 및 개인 투자자 보유 의견.</t>
+          <t>SK하이닉스 GDDR7 기판 공급망 수혜 전망. 주가 변동성에 대한 언급과 함께 외인 매매 동향 주시.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>32100</v>
+        <v>32200</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+8.08%</t>
+          <t>'+8.42%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.62</v>
       </c>
       <c r="E6" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F6" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G6" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="H6" t="n">
         <v>11.3</v>
@@ -978,7 +978,7 @@
         <v>11.92</v>
       </c>
       <c r="O6" t="n">
-        <v>202324553200</v>
+        <v>206402723600</v>
       </c>
       <c r="P6" t="n">
         <v>75900</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>신고점 돌파한 가온전선과 비교되며 주가 상승에 대한 기대감과 하락 우려가 혼재. 단기 3만 5천원 가능성 언급.</t>
+          <t>AI 전력수요 증가 전망 속 거래량 증가 및 상승 분위기 감지. 다만 외인/기관 매도세 및 120일선 돌파 필요성 제기.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['거래량', '상승', '목표가']</t>
+          <t>['AI', '전력수요', '거래량']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6310</v>
+        <v>6280</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+7.68%</t>
+          <t>'+7.17%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.19</v>
       </c>
       <c r="E7" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F7" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G7" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -1070,7 +1070,7 @@
         <v>0.19</v>
       </c>
       <c r="O7" t="n">
-        <v>48156608300</v>
+        <v>49576292810</v>
       </c>
       <c r="P7" t="n">
         <v>13140</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>비트코인 급등 및 가상화폐 테마 확산에 따른 우리기술투자 상승 기대. 공개매수 및 공매도 언급.</t>
+          <t>비트코인 급등 및 가상화폐 테마 강세에 따른 긍정적 전망. 공개매수 및 공매도 세력 관련 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['비트코인', '가상화폐', '공개매수']</t>
+          <t>['비트코인', '가상화폐', '공매도']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1130,13 +1130,13 @@
         <v>-0.09</v>
       </c>
       <c r="E8" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G8" t="n">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="H8" t="n">
         <v>4.86</v>
@@ -1162,7 +1162,7 @@
         <v>4.95</v>
       </c>
       <c r="O8" t="n">
-        <v>44547935760</v>
+        <v>46354663690</v>
       </c>
       <c r="P8" t="n">
         <v>11760</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>기초 체력 강화 및 저평가 인식 속 외인 매도세 관찰. 추석 이후 주가 상승 전망.</t>
+          <t>기초 체력 강화 훈련 및 상승 의지 표명. 외국인 물량 매도에 대한 우려와 호재 뉴스 기대감.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['체력 강화', '외인 매도', '추석']</t>
+          <t>['기초체력', '외국인매도', '호재뉴스']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1222,13 +1222,13 @@
         <v>-0.04</v>
       </c>
       <c r="E9" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F9" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G9" t="n">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="H9" t="n">
         <v>51.73</v>
@@ -1254,7 +1254,7 @@
         <v>25.79</v>
       </c>
       <c r="O9" t="n">
-        <v>47842061750</v>
+        <v>49706932750</v>
       </c>
       <c r="P9" t="n">
         <v>31200</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>국제유가 및 환율 하락 속 주가 상승 기대. JP모간 순매수 확인 및 방산, 드론, 무인기 등 연관 사업 언급.</t>
+          <t>국제유가 및 환율 하락과 함께 방산/드론/무인기 사업 기대감 상승. JP모건 순매수 확인 및 주가 상승 여력 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['국제유가', '환율', 'JP모간']</t>
+          <t>['국제유가', '방산', 'JP모건']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1299,31 +1299,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>331000</v>
+        <v>14080</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.92%</t>
+          <t>'+3.99%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.4</v>
+        <v>-0.34</v>
       </c>
       <c r="E10" t="n">
+        <v>46</v>
+      </c>
+      <c r="F10" t="n">
+        <v>30</v>
+      </c>
+      <c r="G10" t="n">
         <v>78</v>
       </c>
-      <c r="F10" t="n">
-        <v>57</v>
-      </c>
-      <c r="G10" t="n">
-        <v>208</v>
-      </c>
       <c r="H10" t="n">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,47 +1331,47 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>318500</v>
+        <v>13540</v>
       </c>
       <c r="K10" t="n">
-        <v>333000</v>
+        <v>13870</v>
       </c>
       <c r="L10" t="n">
-        <v>349500</v>
+        <v>14650</v>
       </c>
       <c r="M10" t="n">
-        <v>325000</v>
+        <v>13740</v>
       </c>
       <c r="N10" t="n">
-        <v>3.62</v>
+        <v>3.68</v>
       </c>
       <c r="O10" t="n">
-        <v>93872003250</v>
+        <v>79587133430</v>
       </c>
       <c r="P10" t="n">
-        <v>635000</v>
+        <v>20300</v>
       </c>
       <c r="Q10" t="n">
-        <v>52600</v>
+        <v>2885</v>
       </c>
       <c r="R10" t="n">
-        <v>3000</v>
+        <v>236000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>나스닥 폭등 및 구리 가격 상승에 따른 가온전선의 신고가 경신 및 추가 상승 전망. 외인 지분율 확대 및 성장 동력 기대.</t>
+          <t>AI 시대 전력망 관련 주목. 최대주주 소유주식변동 공시 확인. 14,000원대 저항 및 탈출 가능성 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['나스닥', '구리', '신고가']</t>
+          <t>['AI', '전력망', '주식변동']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>006340</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14070</v>
+        <v>331000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+3.91%</t>
+          <t>'+3.92%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.34</v>
+        <v>-0.4</v>
       </c>
       <c r="E11" t="n">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="F11" t="n">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="G11" t="n">
-        <v>72</v>
+        <v>217</v>
       </c>
       <c r="H11" t="n">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,47 +1423,47 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>13540</v>
+        <v>318500</v>
       </c>
       <c r="K11" t="n">
-        <v>13870</v>
+        <v>333000</v>
       </c>
       <c r="L11" t="n">
-        <v>14650</v>
+        <v>349500</v>
       </c>
       <c r="M11" t="n">
-        <v>13740</v>
+        <v>325000</v>
       </c>
       <c r="N11" t="n">
-        <v>3.68</v>
+        <v>3.62</v>
       </c>
       <c r="O11" t="n">
-        <v>78880188340</v>
+        <v>94906293000</v>
       </c>
       <c r="P11" t="n">
-        <v>20300</v>
+        <v>635000</v>
       </c>
       <c r="Q11" t="n">
-        <v>2885</v>
+        <v>52600</v>
       </c>
       <c r="R11" t="n">
-        <v>236000</v>
+        <v>3000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>AI 시대 전력망 중요성 및 모건스탠리 분석 언급. 대한전선과의 비교 및 14000원대 돌파 시도, 연간 영업이익 300억 초과 기대.</t>
+          <t>신고가 경신 및 52주 신고가 돌파 기대감. 나스닥 폭등 및 구리 가격 상승 등 성장 동력 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['AI', '전력망', '영업이익']</t>
+          <t>['신고가', '나스닥', '구리가격']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>000500</t>
         </is>
       </c>
     </row>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10890</v>
+        <v>10850</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+3.22%</t>
+          <t>'+2.84%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>1.01</v>
       </c>
       <c r="E12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G12" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="H12" t="n">
         <v>9.609999999999999</v>
@@ -1530,7 +1530,7 @@
         <v>8.6</v>
       </c>
       <c r="O12" t="n">
-        <v>96448474165</v>
+        <v>100911756970</v>
       </c>
       <c r="P12" t="n">
         <v>11640</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>외인 매도세 속 반등 기대감 및 공매도 논란. 반도체 후공정 테마 언급.</t>
+          <t>반도체 후공정 관련주로 언급. 주가 변동성 및 조정 구간에 대한 의견 교환. 공매도 관련 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['반도체', '후공정', '공매도']</t>
+          <t>['반도체', '후공정', '조정']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13320</v>
+        <v>13280</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.78%</t>
+          <t>'+2.47%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F13" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G13" t="n">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1616,13 +1616,13 @@
         <v>14190</v>
       </c>
       <c r="M13" t="n">
-        <v>13270</v>
+        <v>13250</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>17772662450</v>
+        <v>18200846590</v>
       </c>
       <c r="P13" t="n">
         <v>19380</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>광주 삼성전자 공장 착공 관련 호재 언급. 매출액 증가 및 주포 활동에 대한 기대감과 주의 의견.</t>
+          <t>광주 삼성전자 플렉트 공장 착공 예정. 정정공시 기반 매출액 증가 확인. 일부 투자자 이탈 및 가격 저항 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['삼성전자', '공장 착공', '매출액']</t>
+          <t>['플렉트', '공장착공', '매출액']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1918000</v>
+        <v>1913000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.68%</t>
+          <t>'+2.41%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.06</v>
       </c>
       <c r="E14" t="n">
-        <v>755</v>
+        <v>787</v>
       </c>
       <c r="F14" t="n">
-        <v>459</v>
+        <v>474</v>
       </c>
       <c r="G14" t="n">
-        <v>3412</v>
+        <v>3501</v>
       </c>
       <c r="H14" t="n">
         <v>50.17</v>
@@ -1714,7 +1714,7 @@
         <v>50.23</v>
       </c>
       <c r="O14" t="n">
-        <v>1794612656000</v>
+        <v>1904358682500</v>
       </c>
       <c r="P14" t="n">
         <v>2987000</v>
@@ -1759,31 +1759,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>212500</v>
+        <v>18650</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.16%</t>
+          <t>'+1.97%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.06</v>
+        <v>-0.27</v>
       </c>
       <c r="E15" t="n">
-        <v>41</v>
+        <v>87</v>
       </c>
       <c r="F15" t="n">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="G15" t="n">
-        <v>189</v>
+        <v>359</v>
       </c>
       <c r="H15" t="n">
-        <v>75.5</v>
+        <v>10.47</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>208000</v>
+        <v>18290</v>
       </c>
       <c r="K15" t="n">
-        <v>215000</v>
+        <v>18830</v>
       </c>
       <c r="L15" t="n">
-        <v>215000</v>
+        <v>19540</v>
       </c>
       <c r="M15" t="n">
-        <v>211000</v>
+        <v>18540</v>
       </c>
       <c r="N15" t="n">
-        <v>75.44</v>
+        <v>10.74</v>
       </c>
       <c r="O15" t="n">
-        <v>379737276250</v>
+        <v>75137750250</v>
       </c>
       <c r="P15" t="n">
-        <v>243500</v>
+        <v>40350</v>
       </c>
       <c r="Q15" t="n">
-        <v>64700</v>
+        <v>3320</v>
       </c>
       <c r="R15" t="n">
-        <v>-376000</v>
+        <v>5000</v>
       </c>
       <c r="S15" t="n">
-        <v>12000</v>
+        <v>15000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>배당 기대감 속에 주가 상승 및 21만원 돌파 가능성 언급. 자사주 매입 및 외국인 순매수 시 재진입 고려.</t>
+          <t>체코 원전 수주 관련 긍정적 전망. 수조원 규모 수주 가능성 언급과 함께 공매도 세력에 대한 비판 제기. 연기금 순매수 확인.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['배당', '자사주 매입', '우선주']</t>
+          <t>['원전', '수주', '공매도']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>279500</v>
+        <v>279000</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+2.01%</t>
+          <t>'+1.82%</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1869,10 +1869,10 @@
         <v>800</v>
       </c>
       <c r="F16" t="n">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="G16" t="n">
-        <v>3514</v>
+        <v>3077</v>
       </c>
       <c r="H16" t="n">
         <v>46.56</v>
@@ -1898,7 +1898,7 @@
         <v>46.46</v>
       </c>
       <c r="O16" t="n">
-        <v>1414664226750</v>
+        <v>1476553537250</v>
       </c>
       <c r="P16" t="n">
         <v>374500</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>3분기 역대급 실적 기대감 속 30만 돌파 및 추가 상승 전망. 미국 증시 반도체 대폭등 영향 및 개인 매수세 유입.</t>
+          <t>3분기 역대급 실적 기대감 및 반도체/빅테크주 동반 상승으로 30만원 돌파 전망. AI 낙관론 기반 추세 전환 기대.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['3분기 실적', '반도체', '상승']</t>
+          <t>['실적', '반도체', 'AI']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1943,31 +1943,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18590</v>
+        <v>211500</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+1.64%</t>
+          <t>'+1.68%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.27</v>
+        <v>0.06</v>
       </c>
       <c r="E17" t="n">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="F17" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="G17" t="n">
-        <v>346</v>
+        <v>190</v>
       </c>
       <c r="H17" t="n">
-        <v>10.47</v>
+        <v>75.5</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,51 +1975,51 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>18290</v>
+        <v>208000</v>
       </c>
       <c r="K17" t="n">
-        <v>18830</v>
+        <v>215000</v>
       </c>
       <c r="L17" t="n">
-        <v>19540</v>
+        <v>215000</v>
       </c>
       <c r="M17" t="n">
-        <v>18550</v>
+        <v>211000</v>
       </c>
       <c r="N17" t="n">
-        <v>10.74</v>
+        <v>75.44</v>
       </c>
       <c r="O17" t="n">
-        <v>73558019390</v>
+        <v>400683510000</v>
       </c>
       <c r="P17" t="n">
-        <v>40350</v>
+        <v>243500</v>
       </c>
       <c r="Q17" t="n">
-        <v>3320</v>
+        <v>64700</v>
       </c>
       <c r="R17" t="n">
-        <v>5000</v>
+        <v>-376000</v>
       </c>
       <c r="S17" t="n">
-        <v>15000</v>
+        <v>12000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미국 증시 폭등 속 공매도 관련 불만 제기. 체코 원전 수주 기대감 및 연기금 순매수 확인, 10월 전고점 돌파 전망.</t>
+          <t>배당 기대감 속에 주가 상승 및 21만원 돌파 가능성 언급. 자사주 매입 및 외국인 순매수 시 재진입 고려.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['공매도', '체코 원전', '연기금']</t>
+          <t>['배당', '자사주 매입', '우선주']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,90 +2028,90 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17820</v>
+        <v>86500</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'+0.56%</t>
+          <t>'+0.93%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-1.68</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>128</v>
+        <v>199</v>
       </c>
       <c r="F18" t="n">
-        <v>79</v>
+        <v>131</v>
       </c>
       <c r="G18" t="n">
-        <v>558</v>
+        <v>744</v>
       </c>
       <c r="H18" t="n">
-        <v>6.22</v>
+        <v>23.05</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>17720</v>
+        <v>85700</v>
       </c>
       <c r="K18" t="n">
-        <v>18230</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>18750</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>17500</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>7.9</v>
+        <v>23.12</v>
       </c>
       <c r="O18" t="n">
-        <v>114353753055</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>31500</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1272</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>-359000</v>
+        <v>-160000</v>
       </c>
       <c r="S18" t="n">
-        <v>5000</v>
+        <v>-6000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>미국 광통신 섹터 강세에 따른 대한광통신 추가 상승 기대. 악성 개미 물량 털기 및 숏커버 가능성 언급.</t>
+          <t>SMR 사업 추진 및 공급 계약 체결 확정. 대미 투자 관련 긍정적 뉴스 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['광통신', '미국증시', '숏커버']</t>
+          <t>['SMR', '공급 계약', '대미 투자']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,90 +2120,90 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>85200</v>
+        <v>17800</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-0.12%</t>
+          <t>'+0.45%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.68</v>
       </c>
       <c r="E19" t="n">
-        <v>189</v>
+        <v>131</v>
       </c>
       <c r="F19" t="n">
-        <v>125</v>
+        <v>80</v>
       </c>
       <c r="G19" t="n">
-        <v>705</v>
+        <v>576</v>
       </c>
       <c r="H19" t="n">
-        <v>23.05</v>
+        <v>6.22</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>85300</v>
+        <v>17720</v>
       </c>
       <c r="K19" t="n">
-        <v>87000</v>
+        <v>18230</v>
       </c>
       <c r="L19" t="n">
-        <v>87000</v>
+        <v>18750</v>
       </c>
       <c r="M19" t="n">
-        <v>85200</v>
+        <v>17500</v>
       </c>
       <c r="N19" t="n">
-        <v>23.12</v>
+        <v>7.9</v>
       </c>
       <c r="O19" t="n">
-        <v>62302379900</v>
+        <v>116870511785</v>
       </c>
       <c r="P19" t="n">
-        <v>139200</v>
+        <v>31500</v>
       </c>
       <c r="Q19" t="n">
-        <v>57000</v>
+        <v>1272</v>
       </c>
       <c r="R19" t="n">
-        <v>-160000</v>
+        <v>-359000</v>
       </c>
       <c r="S19" t="n">
-        <v>-6000</v>
+        <v>5000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>SMR 사업 추진 및 공급 계약 체결 확정. 대미 투자 관련 긍정적 뉴스 언급.</t>
+          <t>미국 광통신 섹터 강세에 따른 대한광통신 추가 상승 기대. 악성 개미 물량 털기 및 숏커버 가능성 언급.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['SMR', '공급 계약', '대미 투자']</t>
+          <t>['광통신', '미국증시', '숏커버']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8460</v>
+        <v>8500</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-0.70%</t>
+          <t>'-0.23%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0.01</v>
       </c>
       <c r="E20" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F20" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G20" t="n">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="H20" t="n">
         <v>26.58</v>
@@ -2266,7 +2266,7 @@
         <v>26.57</v>
       </c>
       <c r="O20" t="n">
-        <v>11976418790</v>
+        <v>12542048820</v>
       </c>
       <c r="P20" t="n">
         <v>17950</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>주가 부진 및 무능한 경영에 대한 불만 표출. 외국인 순매도 지속 및 장기 소외, 비전 부재 지적.</t>
+          <t>삼성전자 및 SK하이닉스와의 비교 속 실적 부진 및 주가 소외에 대한 부정적 평가. 외국인 매도세 지속.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['무능', '외국인', '소외']</t>
+          <t>['실적', '주가소외', '외국인매도']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>21100</v>
+        <v>21400</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-1.86%</t>
+          <t>'-0.47%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-0.05</v>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F21" t="n">
         <v>37</v>
       </c>
       <c r="G21" t="n">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H21" t="n">
         <v>1.2</v>
@@ -2358,7 +2358,7 @@
         <v>1.25</v>
       </c>
       <c r="O21" t="n">
-        <v>39485811400</v>
+        <v>40079441825</v>
       </c>
       <c r="P21" t="n">
         <v>22900</v>
@@ -2403,31 +2403,31 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3905</v>
+        <v>24300</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-3.70%</t>
+          <t>'-3.76%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.63</v>
+        <v>1.41</v>
       </c>
       <c r="E22" t="n">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="F22" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="G22" t="n">
-        <v>215</v>
+        <v>154</v>
       </c>
       <c r="H22" t="n">
-        <v>0.96</v>
+        <v>1.76</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,51 +2435,51 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>4055</v>
+        <v>25250</v>
       </c>
       <c r="K22" t="n">
-        <v>4080</v>
+        <v>26150</v>
       </c>
       <c r="L22" t="n">
-        <v>4080</v>
+        <v>26600</v>
       </c>
       <c r="M22" t="n">
-        <v>3850</v>
+        <v>23800</v>
       </c>
       <c r="N22" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="O22" t="n">
-        <v>7353413060</v>
+        <v>86616536375</v>
       </c>
       <c r="P22" t="n">
-        <v>6480</v>
+        <v>39350</v>
       </c>
       <c r="Q22" t="n">
-        <v>1738</v>
+        <v>8200</v>
       </c>
       <c r="R22" t="n">
-        <v>-44000</v>
+        <v>-10000</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>비트코인 회복 소식에도 불구하고 미투온 차트상 하락세 지속 및 신용 물량 털어내기 가능성. 인수 및 스테이블 코인 관련 불확실성.</t>
+          <t>미국 증시 강세와 삼성전자 협업 기대감 언급. 주가 하락세 및 프로그램 매수세 관찰.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['비트코인', '차트분석', '신용물량']</t>
+          <t>['삼성전자', '미국증시', '프로그램매수']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,18 +2488,18 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10610</v>
+        <v>3890</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2507,71 +2507,71 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.4</v>
+        <v>0.63</v>
       </c>
       <c r="E23" t="n">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="F23" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="G23" t="n">
-        <v>165</v>
+        <v>216</v>
       </c>
       <c r="H23" t="n">
-        <v>17.89</v>
+        <v>0.96</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>11060</v>
+        <v>4055</v>
       </c>
       <c r="K23" t="n">
-        <v>10570</v>
+        <v>4080</v>
       </c>
       <c r="L23" t="n">
-        <v>10815</v>
+        <v>4080</v>
       </c>
       <c r="M23" t="n">
-        <v>10060</v>
+        <v>3850</v>
       </c>
       <c r="N23" t="n">
-        <v>18.29</v>
+        <v>0.33</v>
       </c>
       <c r="O23" t="n">
-        <v>29516966690</v>
+        <v>7597252024</v>
       </c>
       <c r="P23" t="n">
-        <v>22450</v>
+        <v>6480</v>
       </c>
       <c r="Q23" t="n">
-        <v>1760</v>
+        <v>1738</v>
       </c>
       <c r="R23" t="n">
-        <v>3000</v>
+        <v>-44000</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>투자경고 종목 지정 및 주가 하락에 대한 불만 표출.</t>
+          <t>비트코인 회복 소식에도 불구하고 미투온 차트상 하락세 지속 및 신용 물량 털어내기 가능성. 인수 및 스테이블 코인 관련 불확실성.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['투자경고', '주가 하락']</t>
+          <t>['비트코인', '차트분석', '신용물량']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,90 +2580,90 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>23850</v>
+        <v>10560</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-5.54%</t>
+          <t>'-4.52%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1.41</v>
+        <v>-0.4</v>
       </c>
       <c r="E24" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F24" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="G24" t="n">
-        <v>128</v>
+        <v>163</v>
       </c>
       <c r="H24" t="n">
-        <v>1.76</v>
+        <v>17.89</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>25250</v>
+        <v>11060</v>
       </c>
       <c r="K24" t="n">
-        <v>26150</v>
+        <v>10570</v>
       </c>
       <c r="L24" t="n">
-        <v>26600</v>
+        <v>10815</v>
       </c>
       <c r="M24" t="n">
-        <v>23800</v>
+        <v>10060</v>
       </c>
       <c r="N24" t="n">
-        <v>0.35</v>
+        <v>18.29</v>
       </c>
       <c r="O24" t="n">
-        <v>84588701925</v>
+        <v>30413357795</v>
       </c>
       <c r="P24" t="n">
-        <v>39350</v>
+        <v>22450</v>
       </c>
       <c r="Q24" t="n">
-        <v>8200</v>
+        <v>1760</v>
       </c>
       <c r="R24" t="n">
-        <v>-10000</v>
+        <v>3000</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>신규 상장 후 변동성, 연상 기대감 대비 하락세. 주포 활동 및 쫄보 매도 언급.</t>
+          <t>투자경고 종목 지정 및 주가 하락 우려. 일부 긍정적 언급 있으나 명확한 근거 부족.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['신규 상장', '주포', '변동성']</t>
+          <t>['투자경고', '주가하락', '저점매수']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>017900</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260922_10.xlsx
+++ b/data/trending_integrated_20260922_10.xlsx
@@ -578,13 +578,13 @@
         <v>0.04</v>
       </c>
       <c r="E2" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="F2" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G2" t="n">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="H2" t="n">
         <v>0.6899999999999999</v>
@@ -610,7 +610,7 @@
         <v>0.65</v>
       </c>
       <c r="O2" t="n">
-        <v>34907734590</v>
+        <v>34928728640</v>
       </c>
       <c r="P2" t="n">
         <v>65300</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>국산 NPU 기반 휴머노이드 개발 착수 및 AI 반도체 파트너십 기대. 로봇 속도 초가속 관련 긍정적 분석.</t>
+          <t>국내 NPU 기반 휴머노이드 개발 착수 및 인텔과의 협력 강화.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['NPU', '휴머노이드', 'AI반도체']</t>
+          <t>['NPU', '휴머노이드', '인텔']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>-0.22</v>
       </c>
       <c r="E3" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F3" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G3" t="n">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="H3" t="n">
         <v>0.48</v>
@@ -702,7 +702,7 @@
         <v>0.7</v>
       </c>
       <c r="O3" t="n">
-        <v>5266455304</v>
+        <v>5269550909</v>
       </c>
       <c r="P3" t="n">
         <v>4760</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>67200</v>
+        <v>66800</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+28.49%</t>
+          <t>'+27.72%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F4" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G4" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H4" t="n">
         <v>6.87</v>
@@ -794,7 +794,7 @@
         <v>6.88</v>
       </c>
       <c r="O4" t="n">
-        <v>117114580150</v>
+        <v>118043694000</v>
       </c>
       <c r="P4" t="n">
         <v>148300</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>반도체 섹터 강세 속 주가 급등 및 키맞추기 기대. 6만원 이상 매도 의견 및 단기 상승 후 하락 가능성 경고.</t>
+          <t>고생 끝에 급등 시현, 심텍과의 비교 속에서 6만원 위 매도 고려. 20일선 안착 및 상한가 기대감.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['반도체', '급등', '키맞추기']</t>
+          <t>['급등', '이격축소', '상한가']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>115850</v>
+        <v>117100</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+13.69%</t>
+          <t>'+14.92%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.12</v>
       </c>
       <c r="E5" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F5" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G5" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H5" t="n">
         <v>18.2</v>
@@ -886,7 +886,7 @@
         <v>18.32</v>
       </c>
       <c r="O5" t="n">
-        <v>239094812650</v>
+        <v>245938930300</v>
       </c>
       <c r="P5" t="n">
         <v>198000</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>SK하이닉스 GDDR7 기판 공급망 수혜 전망. 주가 변동성에 대한 언급과 함께 외인 매매 동향 주시.</t>
+          <t>SK하이닉스 GDDR7 기판 공급망 이슈에 따른 수혜 기대감. 110,000원대 허리 구간에서의 횡보.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['GDDR7', '기판', '수혜']</t>
+          <t>['GDDR7', '수혜', '기판']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>32200</v>
+        <v>32150</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+8.42%</t>
+          <t>'+8.25%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.62</v>
       </c>
       <c r="E6" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F6" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G6" t="n">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="H6" t="n">
         <v>11.3</v>
@@ -978,7 +978,7 @@
         <v>11.92</v>
       </c>
       <c r="O6" t="n">
-        <v>206402723600</v>
+        <v>212106167525</v>
       </c>
       <c r="P6" t="n">
         <v>75900</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>AI 전력수요 증가 전망 속 거래량 증가 및 상승 분위기 감지. 다만 외인/기관 매도세 및 120일선 돌파 필요성 제기.</t>
+          <t>가온전선과의 비교 속에서 급등 기대감 표출. 그러나 외인/기관 매도세와 함께 하락 우려 제기.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['AI', '전력수요', '거래량']</t>
+          <t>['신고점', '거래량', '상승']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6280</v>
+        <v>6220</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+7.17%</t>
+          <t>'+6.14%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1044,7 +1044,7 @@
         <v>47</v>
       </c>
       <c r="G7" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -1070,7 +1070,7 @@
         <v>0.19</v>
       </c>
       <c r="O7" t="n">
-        <v>49576292810</v>
+        <v>51793142785</v>
       </c>
       <c r="P7" t="n">
         <v>13140</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6660</v>
+        <v>6650</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+5.55%</t>
+          <t>'+5.39%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.09</v>
       </c>
       <c r="E8" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F8" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G8" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H8" t="n">
         <v>4.86</v>
@@ -1162,7 +1162,7 @@
         <v>4.95</v>
       </c>
       <c r="O8" t="n">
-        <v>46354663690</v>
+        <v>46622144195</v>
       </c>
       <c r="P8" t="n">
         <v>11760</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30400</v>
+        <v>30300</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+5.37%</t>
+          <t>'+5.03%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.04</v>
       </c>
       <c r="E9" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F9" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G9" t="n">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="H9" t="n">
         <v>51.73</v>
@@ -1254,7 +1254,7 @@
         <v>25.79</v>
       </c>
       <c r="O9" t="n">
-        <v>49706932750</v>
+        <v>51430072375</v>
       </c>
       <c r="P9" t="n">
         <v>31200</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>국제유가 및 환율 하락과 함께 방산/드론/무인기 사업 기대감 상승. JP모건 순매수 확인 및 주가 상승 여력 언급.</t>
+          <t>국제유가 및 환율 하락 속에서 3만원 회복 및 상승 기대감. JP모간 매수세 유입.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['국제유가', '방산', 'JP모건']</t>
+          <t>['국제유가', '환율', '매수세']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14080</v>
+        <v>14070</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.99%</t>
+          <t>'+3.91%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.34</v>
       </c>
       <c r="E10" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F10" t="n">
         <v>30</v>
       </c>
       <c r="G10" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H10" t="n">
         <v>3.34</v>
@@ -1346,7 +1346,7 @@
         <v>3.68</v>
       </c>
       <c r="O10" t="n">
-        <v>79587133430</v>
+        <v>80460445790</v>
       </c>
       <c r="P10" t="n">
         <v>20300</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>AI 시대 전력망 관련 주목. 최대주주 소유주식변동 공시 확인. 14,000원대 저항 및 탈출 가능성 언급.</t>
+          <t>AI 시대 전력망 수혜 기대감 속에서 14000원 저항 구간 돌파 시도. 최대주주 변동 공시 확인.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['AI', '전력망', '주식변동']</t>
+          <t>['AI 시대', '전력망', '공시']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>331000</v>
+        <v>329000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+3.92%</t>
+          <t>'+3.30%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.4</v>
       </c>
       <c r="E11" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F11" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G11" t="n">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="H11" t="n">
         <v>3.22</v>
@@ -1438,7 +1438,7 @@
         <v>3.62</v>
       </c>
       <c r="O11" t="n">
-        <v>94906293000</v>
+        <v>96257512500</v>
       </c>
       <c r="P11" t="n">
         <v>635000</v>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>신고가 경신 및 52주 신고가 돌파 기대감. 나스닥 폭등 및 구리 가격 상승 등 성장 동력 언급.</t>
+          <t>미국 증시 상승과 구리 가격 상승에 따른 52주 신고가 경신 기대.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['신고가', '나스닥', '구리가격']</t>
+          <t>['신고가', '구리 가격', '나스닥']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1483,70 +1483,70 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SFA반도체</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10850</v>
+        <v>13290</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.84%</t>
+          <t>'+2.55%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F12" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G12" t="n">
-        <v>116</v>
+        <v>228</v>
       </c>
       <c r="H12" t="n">
-        <v>9.609999999999999</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>10550</v>
+        <v>12960</v>
       </c>
       <c r="K12" t="n">
-        <v>10730</v>
+        <v>13500</v>
       </c>
       <c r="L12" t="n">
-        <v>11160</v>
+        <v>14190</v>
       </c>
       <c r="M12" t="n">
-        <v>10300</v>
+        <v>13250</v>
       </c>
       <c r="N12" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>100911756970</v>
+        <v>18400209610</v>
       </c>
       <c r="P12" t="n">
-        <v>11640</v>
+        <v>19380</v>
       </c>
       <c r="Q12" t="n">
-        <v>3735</v>
+        <v>3200</v>
       </c>
       <c r="R12" t="n">
-        <v>-140000</v>
+        <v>-40000</v>
       </c>
       <c r="S12" t="n">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>반도체 후공정 관련주로 언급. 주가 변동성 및 조정 구간에 대한 의견 교환. 공매도 관련 언급.</t>
+          <t>광주 삼성전자 플렉트 공장 착공 예정. 정정공시 기반 매출액 증가 확인. 일부 투자자 이탈 및 가격 저항 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['반도체', '후공정', '조정']</t>
+          <t>['플렉트', '공장착공', '매출액']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>036540</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13280</v>
+        <v>18750</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.47%</t>
+          <t>'+2.52%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>-0.27</v>
       </c>
       <c r="E13" t="n">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="F13" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="G13" t="n">
-        <v>224</v>
+        <v>366</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>10.47</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>12960</v>
+        <v>18290</v>
       </c>
       <c r="K13" t="n">
-        <v>13500</v>
+        <v>18830</v>
       </c>
       <c r="L13" t="n">
-        <v>14190</v>
+        <v>19540</v>
       </c>
       <c r="M13" t="n">
-        <v>13250</v>
+        <v>18540</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>10.74</v>
       </c>
       <c r="O13" t="n">
-        <v>18200846590</v>
+        <v>76907772300</v>
       </c>
       <c r="P13" t="n">
-        <v>19380</v>
+        <v>40350</v>
       </c>
       <c r="Q13" t="n">
-        <v>3200</v>
+        <v>3320</v>
       </c>
       <c r="R13" t="n">
-        <v>-40000</v>
+        <v>5000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>광주 삼성전자 플렉트 공장 착공 예정. 정정공시 기반 매출액 증가 확인. 일부 투자자 이탈 및 가격 저항 언급.</t>
+          <t>체코 원전 수주 관련 긍정적 전망. 수조원 규모 수주 가능성 언급과 함께 공매도 세력에 대한 비판 제기. 연기금 순매수 확인.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['플렉트', '공장착공', '매출액']</t>
+          <t>['원전', '수주', '공매도']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1682,13 +1682,13 @@
         <v>-0.06</v>
       </c>
       <c r="E14" t="n">
-        <v>787</v>
+        <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="G14" t="n">
-        <v>3501</v>
+        <v>3428</v>
       </c>
       <c r="H14" t="n">
         <v>50.17</v>
@@ -1714,7 +1714,7 @@
         <v>50.23</v>
       </c>
       <c r="O14" t="n">
-        <v>1904358682500</v>
+        <v>2029156153500</v>
       </c>
       <c r="P14" t="n">
         <v>2987000</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>AI 반도체 주 강세 및 뉴욕 증시 급등에 따른 SK하이닉스 주가 상승 기대.</t>
+          <t>미국 증시 및 반도체주 폭등에 따른 SK하이닉스 200만 돌파 기대감.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['AI', '반도체', '뉴욕증시']</t>
+          <t>['미국 증시', '반도체주', 'FOMO']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1759,31 +1759,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18650</v>
+        <v>212000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+1.97%</t>
+          <t>'+1.92%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.27</v>
+        <v>0.06</v>
       </c>
       <c r="E15" t="n">
-        <v>87</v>
+        <v>42</v>
       </c>
       <c r="F15" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="G15" t="n">
-        <v>359</v>
+        <v>192</v>
       </c>
       <c r="H15" t="n">
-        <v>10.47</v>
+        <v>75.5</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>18290</v>
+        <v>208000</v>
       </c>
       <c r="K15" t="n">
-        <v>18830</v>
+        <v>215000</v>
       </c>
       <c r="L15" t="n">
-        <v>19540</v>
+        <v>215000</v>
       </c>
       <c r="M15" t="n">
-        <v>18540</v>
+        <v>211000</v>
       </c>
       <c r="N15" t="n">
-        <v>10.74</v>
+        <v>75.44</v>
       </c>
       <c r="O15" t="n">
-        <v>75137750250</v>
+        <v>413679271500</v>
       </c>
       <c r="P15" t="n">
-        <v>40350</v>
+        <v>243500</v>
       </c>
       <c r="Q15" t="n">
-        <v>3320</v>
+        <v>64700</v>
       </c>
       <c r="R15" t="n">
-        <v>5000</v>
+        <v>-376000</v>
       </c>
       <c r="S15" t="n">
-        <v>15000</v>
+        <v>12000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>체코 원전 수주 관련 긍정적 전망. 수조원 규모 수주 가능성 언급과 함께 공매도 세력에 대한 비판 제기. 연기금 순매수 확인.</t>
+          <t>배당 기대감 속에 주가 상승 및 21만원 돌파 가능성 언급. 자사주 매입 및 외국인 순매수 시 재진입 고려.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['원전', '수주', '공매도']</t>
+          <t>['배당', '자사주 매입', '우선주']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>279000</v>
+        <v>278750</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+1.82%</t>
+          <t>'+1.73%</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1869,10 +1869,10 @@
         <v>800</v>
       </c>
       <c r="F16" t="n">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="G16" t="n">
-        <v>3077</v>
+        <v>2734</v>
       </c>
       <c r="H16" t="n">
         <v>46.56</v>
@@ -1892,13 +1892,13 @@
         <v>283500</v>
       </c>
       <c r="M16" t="n">
-        <v>279000</v>
+        <v>278500</v>
       </c>
       <c r="N16" t="n">
         <v>46.46</v>
       </c>
       <c r="O16" t="n">
-        <v>1476553537250</v>
+        <v>1566395444750</v>
       </c>
       <c r="P16" t="n">
         <v>374500</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>3분기 역대급 실적 기대감 및 반도체/빅테크주 동반 상승으로 30만원 돌파 전망. AI 낙관론 기반 추세 전환 기대.</t>
+          <t>AI 낙관론 및 미국 반도체 주가 상승에 따른 30만 돌파 및 대폭등 기대감 형성. 3분기 영업이익 발표.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['실적', '반도체', 'AI']</t>
+          <t>['AI 낙관론', '영업이익', '반도체']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1943,79 +1943,79 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>SFA반도체</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>211500</v>
+        <v>10730</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+1.68%</t>
+          <t>'+1.71%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.06</v>
+        <v>1.01</v>
       </c>
       <c r="E17" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="F17" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="G17" t="n">
-        <v>190</v>
+        <v>124</v>
       </c>
       <c r="H17" t="n">
-        <v>75.5</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>208000</v>
+        <v>10550</v>
       </c>
       <c r="K17" t="n">
-        <v>215000</v>
+        <v>10730</v>
       </c>
       <c r="L17" t="n">
-        <v>215000</v>
+        <v>11160</v>
       </c>
       <c r="M17" t="n">
-        <v>211000</v>
+        <v>10300</v>
       </c>
       <c r="N17" t="n">
-        <v>75.44</v>
+        <v>8.6</v>
       </c>
       <c r="O17" t="n">
-        <v>400683510000</v>
+        <v>103823949815</v>
       </c>
       <c r="P17" t="n">
-        <v>243500</v>
+        <v>11640</v>
       </c>
       <c r="Q17" t="n">
-        <v>64700</v>
+        <v>3735</v>
       </c>
       <c r="R17" t="n">
-        <v>-376000</v>
+        <v>-140000</v>
       </c>
       <c r="S17" t="n">
-        <v>12000</v>
+        <v>8000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>배당 기대감 속에 주가 상승 및 21만원 돌파 가능성 언급. 자사주 매입 및 외국인 순매수 시 재진입 고려.</t>
+          <t>외인 매도세와 함께 급락하며 '개잡주'라는 비판 제기. 공매도 마지막 발악이라는 분석.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['배당', '자사주 매입', '우선주']</t>
+          <t>['외인 매도', '급락', '공매도']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2028,90 +2028,90 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>036540</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>86500</v>
+        <v>17800</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'+0.93%</t>
+          <t>'+0.45%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.68</v>
       </c>
       <c r="E18" t="n">
-        <v>199</v>
+        <v>137</v>
       </c>
       <c r="F18" t="n">
-        <v>131</v>
+        <v>82</v>
       </c>
       <c r="G18" t="n">
-        <v>744</v>
+        <v>592</v>
       </c>
       <c r="H18" t="n">
-        <v>23.05</v>
+        <v>6.22</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>85700</v>
+        <v>17720</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>18230</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>18750</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>17500</v>
       </c>
       <c r="N18" t="n">
-        <v>23.12</v>
+        <v>7.9</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>118331683610</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>31500</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1272</v>
       </c>
       <c r="R18" t="n">
-        <v>-160000</v>
+        <v>-359000</v>
       </c>
       <c r="S18" t="n">
-        <v>-6000</v>
+        <v>5000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>SMR 사업 추진 및 공급 계약 체결 확정. 대미 투자 관련 긍정적 뉴스 언급.</t>
+          <t>미국 광통신 주가 상승에 따른 2만원 돌파 기대감. 악성 개미 물량 털기 후 급등 가능성 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['SMR', '공급 계약', '대미 투자']</t>
+          <t>['미국 광통신', '2만원 돌파', '급등']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,90 +2120,90 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17800</v>
+        <v>85600</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'+0.45%</t>
+          <t>'+0.35%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-1.68</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>131</v>
+        <v>209</v>
       </c>
       <c r="F19" t="n">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="G19" t="n">
-        <v>576</v>
+        <v>763</v>
       </c>
       <c r="H19" t="n">
-        <v>6.22</v>
+        <v>23.05</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>17720</v>
+        <v>85300</v>
       </c>
       <c r="K19" t="n">
-        <v>18230</v>
+        <v>87000</v>
       </c>
       <c r="L19" t="n">
-        <v>18750</v>
+        <v>87000</v>
       </c>
       <c r="M19" t="n">
-        <v>17500</v>
+        <v>85200</v>
       </c>
       <c r="N19" t="n">
-        <v>7.9</v>
+        <v>23.12</v>
       </c>
       <c r="O19" t="n">
-        <v>116870511785</v>
+        <v>68975467900</v>
       </c>
       <c r="P19" t="n">
-        <v>31500</v>
+        <v>139200</v>
       </c>
       <c r="Q19" t="n">
-        <v>1272</v>
+        <v>57000</v>
       </c>
       <c r="R19" t="n">
-        <v>-359000</v>
+        <v>-160000</v>
       </c>
       <c r="S19" t="n">
-        <v>5000</v>
+        <v>-6000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>미국 광통신 섹터 강세에 따른 대한광통신 추가 상승 기대. 악성 개미 물량 털기 및 숏커버 가능성 언급.</t>
+          <t>미국 SMR 사업 추진 확정 및 KDDX 전기추진 시스템 공급 계약 체결.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['광통신', '미국증시', '숏커버']</t>
+          <t>['SMR', '공급 계약', 'KDDX']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8500</v>
+        <v>8480</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-0.23%</t>
+          <t>'-0.47%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0.01</v>
       </c>
       <c r="E20" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="F20" t="n">
         <v>36</v>
       </c>
       <c r="G20" t="n">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="H20" t="n">
         <v>26.58</v>
@@ -2266,7 +2266,7 @@
         <v>26.57</v>
       </c>
       <c r="O20" t="n">
-        <v>12542048820</v>
+        <v>12880900850</v>
       </c>
       <c r="P20" t="n">
         <v>17950</v>
@@ -2282,16 +2282,16 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>삼성전자 및 SK하이닉스와의 비교 속 실적 부진 및 주가 소외에 대한 부정적 평가. 외국인 매도세 지속.</t>
+          <t>중국 반도체 부진과 외국인 매도세 속에서 10500원 돌파 기대와 무능한 회사라는 비판 공존.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['실적', '주가소외', '외국인매도']</t>
+          <t>['중국 반도체', '외국인 매도', '적자']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2329,10 +2329,10 @@
         <v>54</v>
       </c>
       <c r="F21" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G21" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="H21" t="n">
         <v>1.2</v>
@@ -2358,7 +2358,7 @@
         <v>1.25</v>
       </c>
       <c r="O21" t="n">
-        <v>40079441825</v>
+        <v>40511193050</v>
       </c>
       <c r="P21" t="n">
         <v>22900</v>
@@ -2374,16 +2374,16 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>모더나 폭등 및 머크 임상 3상 투자 소식에 따른 주가 강세 기대. 외국인 매수세 유입.</t>
+          <t>머크사의 임상 3상 투자 및 외국인 매수세 유입에 따른 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['모더나', '임상 3상', '외국인']</t>
+          <t>['임상 3상', '외국인 매수', '머크']</t>
         </is>
       </c>
       <c r="X21" t="n">
@@ -2407,11 +2407,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>24300</v>
+        <v>24200</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-3.76%</t>
+          <t>'-4.16%</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2424,7 +2424,7 @@
         <v>45</v>
       </c>
       <c r="G22" t="n">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H22" t="n">
         <v>1.76</v>
@@ -2450,7 +2450,7 @@
         <v>0.35</v>
       </c>
       <c r="O22" t="n">
-        <v>86616536375</v>
+        <v>87951652175</v>
       </c>
       <c r="P22" t="n">
         <v>39350</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>미국 증시 강세와 삼성전자 협업 기대감 언급. 주가 하락세 및 프로그램 매수세 관찰.</t>
+          <t>삼성과의 협업 기대감 및 코스닥 역사적 종목 성장 전망.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['삼성전자', '미국증시', '프로그램매수']</t>
+          <t>['삼성', '협업', '코스닥']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2499,11 +2499,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3890</v>
+        <v>3885</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-4.07%</t>
+          <t>'-4.19%</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -2516,7 +2516,7 @@
         <v>40</v>
       </c>
       <c r="G23" t="n">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="H23" t="n">
         <v>0.96</v>
@@ -2542,7 +2542,7 @@
         <v>0.33</v>
       </c>
       <c r="O23" t="n">
-        <v>7597252024</v>
+        <v>7811697066</v>
       </c>
       <c r="P23" t="n">
         <v>6480</v>
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10560</v>
+        <v>10580</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-4.52%</t>
+          <t>'-4.34%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>-0.4</v>
       </c>
       <c r="E24" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F24" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G24" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H24" t="n">
         <v>17.89</v>
@@ -2634,7 +2634,7 @@
         <v>18.29</v>
       </c>
       <c r="O24" t="n">
-        <v>30413357795</v>
+        <v>30921713490</v>
       </c>
       <c r="P24" t="n">
         <v>22450</v>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>투자경고 종목 지정 및 주가 하락 우려. 일부 긍정적 언급 있으나 명확한 근거 부족.</t>
+          <t>투자경고 종목 지정 속에서 11000원 돌파 기대와 함께 차트 붕괴 및 급락 우려 공존. 종가 양전 시도.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['투자경고', '주가하락', '저점매수']</t>
+          <t>['투자경고', '돌파', '차트']</t>
         </is>
       </c>
       <c r="X24" t="n">
